--- a/anonymized_data/crm_anonymized_data.xlsx
+++ b/anonymized_data/crm_anonymized_data.xlsx
@@ -2886,12 +2886,12 @@
       </c>
       <c r="H2" s="7" t="inlineStr">
         <is>
-          <t>Paulbury</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="I2" s="7" t="inlineStr">
         <is>
-          <t>college</t>
+          <t>other</t>
         </is>
       </c>
       <c r="J2" s="11" t="n">
@@ -2933,7 +2933,7 @@
       </c>
       <c r="H3" s="8" t="inlineStr">
         <is>
-          <t>Christinaland</t>
+          <t>Houston</t>
         </is>
       </c>
       <c r="I3" s="8" t="inlineStr">
@@ -2980,12 +2980,12 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>Tylerborough</t>
+          <t>Washington D.C.</t>
         </is>
       </c>
       <c r="I4" s="7" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>other</t>
         </is>
       </c>
       <c r="J4" s="11" t="n">
@@ -3027,12 +3027,12 @@
       </c>
       <c r="H5" s="12" t="inlineStr">
         <is>
-          <t>New Travis</t>
+          <t>Houston</t>
         </is>
       </c>
       <c r="I5" s="7" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>college</t>
         </is>
       </c>
       <c r="J5" s="19" t="n">
@@ -3074,7 +3074,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>Joseshire</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="I6" s="8" t="inlineStr">
@@ -3121,12 +3121,12 @@
       </c>
       <c r="H7" s="8" t="inlineStr">
         <is>
-          <t>Millerland</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="I7" s="8" t="inlineStr">
         <is>
-          <t>cold outreach</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="J7" s="19" t="n">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>West Oliviashire</t>
+          <t>Chicago</t>
         </is>
       </c>
       <c r="I8" s="7" t="inlineStr">
         <is>
-          <t>cold outreach</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="J8" s="11" t="n">
@@ -3215,12 +3215,12 @@
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>Williamton</t>
+          <t>Chicago</t>
         </is>
       </c>
       <c r="I9" s="8" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>life</t>
         </is>
       </c>
       <c r="J9" s="19" t="n">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>North Christina</t>
+          <t>Washington D.C.</t>
         </is>
       </c>
       <c r="I10" s="7" t="inlineStr">
         <is>
-          <t>college</t>
+          <t>cold outreach</t>
         </is>
       </c>
       <c r="J10" s="11" t="n">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
-          <t>Lisaberg</t>
+          <t>Chicago</t>
         </is>
       </c>
       <c r="I11" s="8" t="inlineStr">
         <is>
-          <t>college</t>
+          <t>life</t>
         </is>
       </c>
       <c r="J11" s="19" t="n">
@@ -3356,12 +3356,12 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>Johnsonport</t>
+          <t>Washington D.C.</t>
         </is>
       </c>
       <c r="I12" s="7" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>cold outreach</t>
         </is>
       </c>
       <c r="J12" s="7" t="n"/>
@@ -3401,12 +3401,12 @@
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
-          <t>West Austinview</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="I13" s="8" t="inlineStr">
         <is>
-          <t>referral</t>
+          <t>college</t>
         </is>
       </c>
       <c r="J13" s="19" t="n">
@@ -3448,12 +3448,12 @@
       </c>
       <c r="H14" s="7" t="inlineStr">
         <is>
-          <t>New Jenniferborough</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="I14" s="7" t="inlineStr">
         <is>
-          <t>life</t>
+          <t>referral</t>
         </is>
       </c>
       <c r="J14" s="19" t="n">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="H15" s="8" t="inlineStr">
         <is>
-          <t>Lake Richardfurt</t>
+          <t>Washington D.C.</t>
         </is>
       </c>
       <c r="I15" s="8" t="inlineStr">
         <is>
-          <t>cold outreach</t>
+          <t>life</t>
         </is>
       </c>
       <c r="J15" s="19" t="n">
@@ -3542,12 +3542,12 @@
       </c>
       <c r="H16" s="8" t="inlineStr">
         <is>
-          <t>Howardtown</t>
+          <t>Houston</t>
         </is>
       </c>
       <c r="I16" s="7" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>life</t>
         </is>
       </c>
       <c r="J16" s="11" t="n">
@@ -3587,12 +3587,12 @@
       </c>
       <c r="H17" s="7" t="inlineStr">
         <is>
-          <t>Lake Alexanderland</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="I17" s="8" t="inlineStr">
         <is>
-          <t>cold outreach</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="J17" s="19" t="n">
@@ -3634,12 +3634,12 @@
       </c>
       <c r="H18" s="8" t="inlineStr">
         <is>
-          <t>Elizabethland</t>
+          <t>Washington D.C.</t>
         </is>
       </c>
       <c r="I18" s="7" t="inlineStr">
         <is>
-          <t>life</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="J18" s="11" t="n">
@@ -3679,12 +3679,12 @@
       </c>
       <c r="H19" s="7" t="inlineStr">
         <is>
-          <t>Mcdonaldhaven</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="I19" s="8" t="inlineStr">
         <is>
-          <t>life</t>
+          <t>other</t>
         </is>
       </c>
       <c r="J19" s="19" t="n">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H20" s="7" t="inlineStr">
         <is>
-          <t>North Michaelview</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="I20" s="7" t="inlineStr">
         <is>
-          <t>referral</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="J20" s="19" t="n">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="H21" s="8" t="inlineStr">
         <is>
-          <t>New Danielland</t>
+          <t>Houston</t>
         </is>
       </c>
       <c r="I21" s="8" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>life</t>
         </is>
       </c>
       <c r="J21" s="19" t="n">
@@ -3818,12 +3818,12 @@
       </c>
       <c r="H22" s="7" t="inlineStr">
         <is>
-          <t>Jacquelineland</t>
+          <t>Chicago</t>
         </is>
       </c>
       <c r="I22" s="7" t="inlineStr">
         <is>
-          <t>life</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="J22" s="11" t="n">
@@ -3865,7 +3865,7 @@
       </c>
       <c r="H23" s="8" t="inlineStr">
         <is>
-          <t>Brendabury</t>
+          <t>Washington D.C.</t>
         </is>
       </c>
       <c r="I23" s="8" t="inlineStr">
@@ -3912,12 +3912,12 @@
       </c>
       <c r="H24" s="7" t="inlineStr">
         <is>
-          <t>West Robert</t>
+          <t>Washington D.C.</t>
         </is>
       </c>
       <c r="I24" s="7" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="J24" s="7" t="n"/>
@@ -3957,7 +3957,7 @@
       </c>
       <c r="H25" s="8" t="inlineStr">
         <is>
-          <t>Cooperberg</t>
+          <t>Washington D.C.</t>
         </is>
       </c>
       <c r="I25" s="8" t="inlineStr">
@@ -4004,12 +4004,12 @@
       </c>
       <c r="H26" s="7" t="inlineStr">
         <is>
-          <t>Lisahaven</t>
+          <t>Washington D.C.</t>
         </is>
       </c>
       <c r="I26" s="7" t="inlineStr">
         <is>
-          <t>cold outreach</t>
+          <t>referral</t>
         </is>
       </c>
       <c r="J26" s="11" t="n">
@@ -4051,12 +4051,12 @@
       </c>
       <c r="H27" s="8" t="inlineStr">
         <is>
-          <t>South Natalie</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="I27" s="8" t="inlineStr">
         <is>
-          <t>cold outreach</t>
+          <t>referral</t>
         </is>
       </c>
       <c r="J27" s="8" t="n"/>
@@ -6416,7 +6416,7 @@
         <v>3</v>
       </c>
       <c r="C2" s="11" t="n">
-        <v>46310</v>
+        <v>45991</v>
       </c>
       <c r="D2" s="7" t="inlineStr">
         <is>
@@ -6425,12 +6425,12 @@
       </c>
       <c r="E2" s="17" t="inlineStr">
         <is>
-          <t>Enough everybody air nature name.</t>
+          <t>As majority those decide bad answer group.</t>
         </is>
       </c>
       <c r="F2" s="17" t="inlineStr">
         <is>
-          <t>Accept where direction at.</t>
+          <t>Return life raise improve.</t>
         </is>
       </c>
       <c r="G2" s="7" t="n"/>
@@ -6443,7 +6443,7 @@
         <v>4</v>
       </c>
       <c r="C3" s="19" t="n">
-        <v>45676</v>
+        <v>46120</v>
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
@@ -6452,12 +6452,12 @@
       </c>
       <c r="E3" s="8" t="inlineStr">
         <is>
-          <t>Down store technology enough.</t>
+          <t>Computer fill property down get.</t>
         </is>
       </c>
       <c r="F3" s="8" t="inlineStr">
         <is>
-          <t>After particularly where grow write leave pull trip.</t>
+          <t>Important central cut cause get audience.</t>
         </is>
       </c>
       <c r="G3" s="8" t="n"/>
@@ -6470,21 +6470,21 @@
         <v>7</v>
       </c>
       <c r="C4" s="11" t="n">
-        <v>46377</v>
+        <v>46128</v>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>thank you</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>Matter begin third style detail project control.</t>
+          <t>Side foot home show threat recently audience.</t>
         </is>
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>Mean notice name left.</t>
+          <t>Enter exist close there natural east appear.</t>
         </is>
       </c>
       <c r="G4" s="7" t="n"/>
@@ -6497,16 +6497,16 @@
         <v>7</v>
       </c>
       <c r="C5" s="11" t="n">
-        <v>45794</v>
+        <v>45834</v>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>thank you</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>Like week six maybe seat with.</t>
+          <t>Air nature name yes factor accept where.</t>
         </is>
       </c>
       <c r="F5" s="8" t="n"/>
@@ -6520,21 +6520,21 @@
         <v>8</v>
       </c>
       <c r="C6" s="23" t="n">
-        <v>46348</v>
+        <v>45862</v>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>thank you</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>Similar believe Republican know her involve first clear.</t>
+          <t>Heart down store technology.</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>Sound language for child usually trip other.</t>
+          <t>Almost after particularly.</t>
         </is>
       </c>
       <c r="G6" s="7" t="n"/>
@@ -6547,7 +6547,7 @@
         <v>9</v>
       </c>
       <c r="C7" s="19" t="n">
-        <v>45960</v>
+        <v>45729</v>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
@@ -6556,12 +6556,12 @@
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>White suddenly particularly area their stock inside mouth.</t>
+          <t>Spring in interview one fine matter.</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>Tend majority blood ago rich piece.</t>
+          <t>Detail project control unit around mean notice name.</t>
         </is>
       </c>
       <c r="G7" s="8" t="n"/>
@@ -6574,21 +6574,21 @@
         <v>10</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>45689</v>
+        <v>45794</v>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>thank you</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>Sea stage somebody keep seek defense offer.</t>
+          <t>Break like week six maybe seat with.</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>Structure mean store require position special agree.</t>
+          <t>Similar believe Republican know her involve first clear.</t>
         </is>
       </c>
       <c r="G8" s="7" t="n"/>
@@ -6601,21 +6601,21 @@
         <v>8</v>
       </c>
       <c r="C9" s="19" t="n">
-        <v>46232</v>
+        <v>46102</v>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>Apply action offer ok design fire.</t>
+          <t>Me after middle deep scientist.</t>
         </is>
       </c>
       <c r="F9" s="8" t="inlineStr">
         <is>
-          <t>Three occur painting.</t>
+          <t>Rate up painting save popular other along matter.</t>
         </is>
       </c>
       <c r="G9" s="8" t="n"/>
@@ -6628,16 +6628,16 @@
         <v>9</v>
       </c>
       <c r="C10" s="11" t="n">
-        <v>46204</v>
+        <v>46153</v>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>thank you</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>Stock many stage.</t>
+          <t>Inside mouth home himself.</t>
         </is>
       </c>
       <c r="F10" s="7" t="n"/>
@@ -6651,16 +6651,16 @@
         <v>10</v>
       </c>
       <c r="C11" s="19" t="n">
-        <v>46331</v>
+        <v>46235</v>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>call</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>Rich treat if different out want.</t>
+          <t>Different three serve read.</t>
         </is>
       </c>
       <c r="F11" s="8" t="n"/>
@@ -6674,21 +6674,21 @@
         <v>11</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>45885</v>
+        <v>46104</v>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>in person</t>
+          <t>call</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>Late power fill indicate often cell.</t>
+          <t>Somebody keep seek defense.</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>Significant race reduce market.</t>
+          <t>Test morning structure.</t>
         </is>
       </c>
       <c r="G12" s="7" t="n"/>
@@ -6701,21 +6701,21 @@
         <v>12</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>46383</v>
+        <v>45666</v>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>in person</t>
+          <t>thank you</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>Beyond pick former same.</t>
+          <t>Word space head case after last apply.</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>Rock low professional wrong.</t>
+          <t>Ok design fire.</t>
         </is>
       </c>
       <c r="G13" s="8" t="n"/>
@@ -6728,21 +6728,21 @@
         <v>14</v>
       </c>
       <c r="C14" s="11" t="n">
-        <v>46367</v>
+        <v>45689</v>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>thank you</t>
+          <t>call</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>Practice manager eye foreign history.</t>
+          <t>Three occur painting.</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
-          <t>Ok rate consider leave have office.</t>
+          <t>Candidate center story guess white tend here.</t>
         </is>
       </c>
       <c r="G14" s="7" t="n"/>
@@ -6755,21 +6755,21 @@
         <v>17</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>45734</v>
+        <v>45964</v>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>in person</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>Air into successful lose positive someone there.</t>
+          <t>Out want world arrive suggest.</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>Indeed wear hundred Republican finish suffer game.</t>
+          <t>Far agent right policy enter.</t>
         </is>
       </c>
       <c r="G15" s="8" t="n"/>
@@ -6782,21 +6782,21 @@
         <v>13</v>
       </c>
       <c r="C16" s="11" t="n">
-        <v>46091</v>
+        <v>45767</v>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>email</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>Two within director beautiful page.</t>
+          <t>Significant race reduce market.</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
-          <t>Of wrong run kitchen similar interest front.</t>
+          <t>Pick former same various call fight.</t>
         </is>
       </c>
       <c r="G16" s="7" t="n"/>
@@ -6809,21 +6809,21 @@
         <v>13</v>
       </c>
       <c r="C17" s="19" t="n">
-        <v>46374</v>
+        <v>45879</v>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
         <is>
-          <t>Degree build despite human successful.</t>
+          <t>Professional wrong discuss between environment debate.</t>
         </is>
       </c>
       <c r="F17" s="8" t="inlineStr">
         <is>
-          <t>Pm little walk.</t>
+          <t>Tree game friend treat economic improve child trade.</t>
         </is>
       </c>
       <c r="G17" s="8" t="n"/>
@@ -6836,21 +6836,21 @@
         <v>13</v>
       </c>
       <c r="C18" s="11" t="n">
-        <v>45900</v>
+        <v>45842</v>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>thank you</t>
+          <t>other</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>Probably protect type we student community general.</t>
+          <t>Thought myself usually.</t>
         </is>
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
-          <t>Even young suggest happen.</t>
+          <t>Someone there between laugh event allow middle finish.</t>
         </is>
       </c>
       <c r="G18" s="7" t="n"/>
@@ -6863,21 +6863,21 @@
         <v>12</v>
       </c>
       <c r="C19" s="19" t="n">
-        <v>46024</v>
+        <v>46349</v>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>call</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t>Scene simple peace them.</t>
+          <t>Suffer game short town two.</t>
         </is>
       </c>
       <c r="F19" s="8" t="inlineStr">
         <is>
-          <t>From system recognize enjoy place possible station senior.</t>
+          <t>Beautiful page newspaper read of wrong run.</t>
         </is>
       </c>
       <c r="G19" s="8" t="n"/>
@@ -6890,21 +6890,21 @@
         <v>21</v>
       </c>
       <c r="C20" s="11" t="n">
-        <v>46170</v>
+        <v>45828</v>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>in person</t>
+          <t>thank you</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>Throw former bar fact mind in.</t>
+          <t>Attorney own movement history degree build.</t>
         </is>
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
-          <t>Appear form lot none glass guy city.</t>
+          <t>Low make window whole result analysis.</t>
         </is>
       </c>
       <c r="G20" s="7" t="n"/>
@@ -6917,21 +6917,21 @@
         <v>23</v>
       </c>
       <c r="C21" s="19" t="n">
-        <v>46173</v>
+        <v>46375</v>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>email</t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t>Her as let coach kind.</t>
+          <t>Little walk several probably protect.</t>
         </is>
       </c>
       <c r="F21" s="8" t="inlineStr">
         <is>
-          <t>Doctor mission exactly me just drive.</t>
+          <t>Can instead method even.</t>
         </is>
       </c>
       <c r="G21" s="8" t="n"/>
@@ -6944,21 +6944,21 @@
         <v>23</v>
       </c>
       <c r="C22" s="11" t="n">
-        <v>46213</v>
+        <v>46024</v>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>other</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>Small conference PM white learn animal.</t>
+          <t>Suggest happen size scene simple peace them.</t>
         </is>
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
-          <t>Dinner agree shoulder prove water color.</t>
+          <t>From system recognize enjoy place possible station senior.</t>
         </is>
       </c>
       <c r="G22" s="7" t="n"/>
@@ -6971,7 +6971,7 @@
         <v>23</v>
       </c>
       <c r="C23" s="19" t="n">
-        <v>46216</v>
+        <v>46170</v>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>Full better hotel nearly answer institution.</t>
+          <t>Throw former bar fact mind in.</t>
         </is>
       </c>
       <c r="F23" s="8" t="n"/>
@@ -6994,16 +6994,16 @@
         <v>25</v>
       </c>
       <c r="C24" s="11" t="n">
-        <v>45928</v>
+        <v>45886</v>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>Onto near lay.</t>
+          <t>Appear form lot none glass guy city.</t>
         </is>
       </c>
       <c r="F24" s="7" t="n"/>
@@ -7017,16 +7017,16 @@
         <v>24</v>
       </c>
       <c r="C25" s="19" t="n">
-        <v>46247</v>
+        <v>46378</v>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>thank you</t>
+          <t>other</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t>Wide two against measure space relate rate.</t>
+          <t>Task rise arrive prevent.</t>
         </is>
       </c>
       <c r="F25" s="8" t="n"/>
@@ -7040,21 +7040,21 @@
         <v>2</v>
       </c>
       <c r="C26" s="11" t="n">
-        <v>45898</v>
+        <v>45961</v>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>email</t>
         </is>
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>Most life activity second.</t>
+          <t>Doctor mission exactly me just drive.</t>
         </is>
       </c>
       <c r="F26" s="7" t="inlineStr">
         <is>
-          <t>Help would indeed brother sport at.</t>
+          <t>Visit suggest statement find.</t>
         </is>
       </c>
       <c r="G26" s="7" t="n"/>
@@ -7067,21 +7067,21 @@
         <v>24</v>
       </c>
       <c r="C27" s="19" t="n">
-        <v>45783</v>
+        <v>46255</v>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr">
         <is>
-          <t>Design over leader indeed.</t>
+          <t>Song dinner agree.</t>
         </is>
       </c>
       <c r="F27" s="8" t="inlineStr">
         <is>
-          <t>Charge spring report take these point east fight.</t>
+          <t>Water color game name you.</t>
         </is>
       </c>
       <c r="G27" s="8" t="n"/>
@@ -7094,16 +7094,16 @@
         <v>24</v>
       </c>
       <c r="C28" s="19" t="n">
-        <v>46031</v>
+        <v>46012</v>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>thank you</t>
+          <t>email</t>
         </is>
       </c>
       <c r="E28" s="8" t="inlineStr">
         <is>
-          <t>Include fly soon voice tree.</t>
+          <t>Every tonight point friend support onto near.</t>
         </is>
       </c>
       <c r="F28" s="8" t="n"/>

--- a/anonymized_data/crm_anonymized_data.xlsx
+++ b/anonymized_data/crm_anonymized_data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" tabRatio="600" firstSheet="1" activeTab="3" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="1" activeTab="3" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" state="visible" r:id="rId1"/>
@@ -12,7 +12,9 @@
     <sheet name="Interactions" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Referrals" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Interactions'!$A$1:$H$201</definedName>
+  </definedNames>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -127,7 +129,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -187,6 +189,13 @@
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -920,22 +929,22 @@
       </c>
       <c r="B2" s="7" t="inlineStr">
         <is>
-          <t>Graves, Gomez and Marquez</t>
+          <t>Smith-Davis</t>
         </is>
       </c>
       <c r="C2" s="7" t="inlineStr">
         <is>
-          <t>Manufacturing</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D2" s="7" t="inlineStr">
         <is>
-          <t>https://www.gravesgomezandm.com</t>
+          <t>https://www.smith-davis.com</t>
         </is>
       </c>
       <c r="E2" s="7" t="inlineStr">
         <is>
-          <t>Baby return likely let should.</t>
+          <t>Approach something detail strategy stand TV instead issue.</t>
         </is>
       </c>
       <c r="F2" s="7" t="n"/>
@@ -946,22 +955,22 @@
       </c>
       <c r="B3" s="8" t="inlineStr">
         <is>
-          <t>Davis and Sons</t>
+          <t>Marquez-Castillo</t>
         </is>
       </c>
       <c r="C3" s="8" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D3" s="8" t="inlineStr">
         <is>
-          <t>https://www.davisandsons.com</t>
+          <t>https://www.marquez-castill.com</t>
         </is>
       </c>
       <c r="E3" s="8" t="inlineStr">
         <is>
-          <t>Voice different its today.</t>
+          <t>At charge certainly.</t>
         </is>
       </c>
       <c r="F3" s="8" t="n"/>
@@ -972,17 +981,17 @@
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Alexander and Sons</t>
+          <t>Martin, Sims and Kemp</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>https://www.alexanderandson.com</t>
+          <t>https://www.martinsimsandke.com</t>
         </is>
       </c>
       <c r="E4" s="7" t="n"/>
@@ -994,17 +1003,17 @@
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>Phelps LLC</t>
+          <t>Johnson-Sims</t>
         </is>
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>https://www.phelpsllc.com</t>
+          <t>https://www.johnson-sims.com</t>
         </is>
       </c>
       <c r="E5" s="8" t="n"/>
@@ -1016,17 +1025,17 @@
       </c>
       <c r="B6" s="17" t="inlineStr">
         <is>
-          <t>Ochoa Inc</t>
+          <t>Mckinney-Juarez</t>
         </is>
       </c>
       <c r="C6" s="17" t="inlineStr">
         <is>
-          <t>Manufacturing</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>https://www.ochoainc.com</t>
+          <t>https://www.mckinney-juarez.com</t>
         </is>
       </c>
       <c r="E6" s="7" t="n"/>
@@ -1038,17 +1047,17 @@
       </c>
       <c r="B7" s="18" t="inlineStr">
         <is>
-          <t>Rodriguez, Thomas and Freeman</t>
+          <t>Adams, Blackwell and Wilson</t>
         </is>
       </c>
       <c r="C7" s="18" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>https://www.rodriguezthomas.com</t>
+          <t>https://www.adamsblackwella.com</t>
         </is>
       </c>
       <c r="E7" s="8" t="n"/>
@@ -1060,7 +1069,7 @@
       </c>
       <c r="B8" s="17" t="inlineStr">
         <is>
-          <t>Garcia, Baker and Banks</t>
+          <t>Torres, Jones and Kelly</t>
         </is>
       </c>
       <c r="C8" s="17" t="inlineStr">
@@ -1070,12 +1079,12 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>https://www.garciabakerandb.com</t>
+          <t>https://www.torresjonesandk.com</t>
         </is>
       </c>
       <c r="E8" s="17" t="inlineStr">
         <is>
-          <t>Long test wife sing although.</t>
+          <t>Past safe hand defense.</t>
         </is>
       </c>
       <c r="F8" s="7" t="n"/>
@@ -1086,7 +1095,7 @@
       </c>
       <c r="B9" s="18" t="inlineStr">
         <is>
-          <t>Sanchez, Powell and Thompson</t>
+          <t>Todd-Reynolds</t>
         </is>
       </c>
       <c r="C9" s="18" t="inlineStr">
@@ -1096,7 +1105,7 @@
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>https://www.sanchezpowellan.com</t>
+          <t>https://www.todd-reynolds.com</t>
         </is>
       </c>
       <c r="E9" s="8" t="n"/>
@@ -1108,17 +1117,17 @@
       </c>
       <c r="B10" s="17" t="inlineStr">
         <is>
-          <t>Brown Group</t>
+          <t>Rogers and Sons</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Manufacturing</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>https://www.browngroup.com</t>
+          <t>https://www.rogersandsons.com</t>
         </is>
       </c>
       <c r="E10" s="7" t="n"/>
@@ -1130,17 +1139,17 @@
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>Rosario, Owens and Tucker</t>
+          <t>Mclean, Stanley and Howard</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Manufacturing</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>https://www.rosarioowensand.com</t>
+          <t>https://www.mcleanstanleyan.com</t>
         </is>
       </c>
       <c r="E11" s="8" t="n"/>
@@ -1152,17 +1161,17 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Mcmahon-Brown</t>
+          <t>Thomas-Green</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>Retail</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>https://www.mcmahon-brown.com</t>
+          <t>https://www.thomas-green.com</t>
         </is>
       </c>
       <c r="E12" s="7" t="n"/>
@@ -1174,17 +1183,17 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>Shea-Gonzalez</t>
+          <t>Kennedy, Ramirez and Richardson</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>https://www.shea-gonzalez.com</t>
+          <t>https://www.kennedyramireza.com</t>
         </is>
       </c>
       <c r="E13" s="8" t="n"/>
@@ -1196,22 +1205,22 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Stevenson, Smith and Burke</t>
+          <t>Ortiz-Murphy</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Retail</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>https://www.stevensonsmitha.com</t>
+          <t>https://www.ortiz-murphy.com</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>Recognize serious it available approach PM.</t>
+          <t>Explain single industry let value realize.</t>
         </is>
       </c>
       <c r="F14" s="7" t="n"/>
@@ -1222,17 +1231,17 @@
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>Brown-Smith</t>
+          <t>Fields Ltd</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Retail</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>https://www.brown-smith.com</t>
+          <t>https://www.fieldsltd.com</t>
         </is>
       </c>
       <c r="E15" s="8" t="n"/>
@@ -1244,17 +1253,17 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Mercado Group</t>
+          <t>Haynes-Guerra</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>https://www.mercadogroup.com</t>
+          <t>https://www.haynes-guerra.com</t>
         </is>
       </c>
       <c r="E16" s="7" t="n"/>
@@ -1266,17 +1275,17 @@
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>Morgan-Sullivan</t>
+          <t>Mitchell, Jackson and Fisher</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>https://www.morgan-sullivan.com</t>
+          <t>https://www.mitchelljackson.com</t>
         </is>
       </c>
       <c r="E17" s="8" t="n"/>
@@ -1288,17 +1297,17 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Bentley Group</t>
+          <t>Arias LLC</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Retail</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>https://www.bentleygroup.com</t>
+          <t>https://www.ariasllc.com</t>
         </is>
       </c>
       <c r="E18" s="7" t="n"/>
@@ -2886,12 +2895,12 @@
       </c>
       <c r="H2" s="7" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Chicago</t>
         </is>
       </c>
       <c r="I2" s="7" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="J2" s="11" t="n">
@@ -2933,12 +2942,12 @@
       </c>
       <c r="H3" s="8" t="inlineStr">
         <is>
-          <t>Houston</t>
+          <t>Chicago</t>
         </is>
       </c>
       <c r="I3" s="8" t="inlineStr">
         <is>
-          <t>college</t>
+          <t>life</t>
         </is>
       </c>
       <c r="J3" s="11" t="n">
@@ -2985,7 +2994,7 @@
       </c>
       <c r="I4" s="7" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>cold outreach</t>
         </is>
       </c>
       <c r="J4" s="11" t="n">
@@ -3027,12 +3036,12 @@
       </c>
       <c r="H5" s="12" t="inlineStr">
         <is>
-          <t>Houston</t>
+          <t>Chicago</t>
         </is>
       </c>
       <c r="I5" s="7" t="inlineStr">
         <is>
-          <t>college</t>
+          <t>life</t>
         </is>
       </c>
       <c r="J5" s="19" t="n">
@@ -3074,12 +3083,12 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Washington D.C.</t>
         </is>
       </c>
       <c r="I6" s="8" t="inlineStr">
         <is>
-          <t>college</t>
+          <t>cold outreach</t>
         </is>
       </c>
       <c r="J6" s="11" t="n">
@@ -3121,12 +3130,12 @@
       </c>
       <c r="H7" s="8" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="I7" s="8" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>college</t>
         </is>
       </c>
       <c r="J7" s="19" t="n">
@@ -3168,12 +3177,12 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>Chicago</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="I8" s="7" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>referral</t>
         </is>
       </c>
       <c r="J8" s="11" t="n">
@@ -3215,7 +3224,7 @@
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>Chicago</t>
+          <t>Washington D.C.</t>
         </is>
       </c>
       <c r="I9" s="8" t="inlineStr">
@@ -3262,12 +3271,12 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>Washington D.C.</t>
+          <t>Houston</t>
         </is>
       </c>
       <c r="I10" s="7" t="inlineStr">
         <is>
-          <t>cold outreach</t>
+          <t>life</t>
         </is>
       </c>
       <c r="J10" s="11" t="n">
@@ -3309,12 +3318,12 @@
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
-          <t>Chicago</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="I11" s="8" t="inlineStr">
         <is>
-          <t>life</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="J11" s="19" t="n">
@@ -3361,7 +3370,7 @@
       </c>
       <c r="I12" s="7" t="inlineStr">
         <is>
-          <t>cold outreach</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="J12" s="7" t="n"/>
@@ -3406,7 +3415,7 @@
       </c>
       <c r="I13" s="8" t="inlineStr">
         <is>
-          <t>college</t>
+          <t>other</t>
         </is>
       </c>
       <c r="J13" s="19" t="n">
@@ -3448,12 +3457,12 @@
       </c>
       <c r="H14" s="7" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="I14" s="7" t="inlineStr">
         <is>
-          <t>referral</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="J14" s="19" t="n">
@@ -3495,7 +3504,7 @@
       </c>
       <c r="H15" s="8" t="inlineStr">
         <is>
-          <t>Washington D.C.</t>
+          <t>Houston</t>
         </is>
       </c>
       <c r="I15" s="8" t="inlineStr">
@@ -3542,12 +3551,12 @@
       </c>
       <c r="H16" s="8" t="inlineStr">
         <is>
-          <t>Houston</t>
+          <t>Chicago</t>
         </is>
       </c>
       <c r="I16" s="7" t="inlineStr">
         <is>
-          <t>life</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="J16" s="11" t="n">
@@ -3587,12 +3596,12 @@
       </c>
       <c r="H17" s="7" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Washington D.C.</t>
         </is>
       </c>
       <c r="I17" s="8" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>other</t>
         </is>
       </c>
       <c r="J17" s="19" t="n">
@@ -3679,12 +3688,12 @@
       </c>
       <c r="H19" s="7" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Washington D.C.</t>
         </is>
       </c>
       <c r="I19" s="8" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>referral</t>
         </is>
       </c>
       <c r="J19" s="19" t="n">
@@ -3724,12 +3733,12 @@
       </c>
       <c r="H20" s="7" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Washington D.C.</t>
         </is>
       </c>
       <c r="I20" s="7" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>referral</t>
         </is>
       </c>
       <c r="J20" s="19" t="n">
@@ -3771,12 +3780,12 @@
       </c>
       <c r="H21" s="8" t="inlineStr">
         <is>
-          <t>Houston</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="I21" s="8" t="inlineStr">
         <is>
-          <t>life</t>
+          <t>referral</t>
         </is>
       </c>
       <c r="J21" s="19" t="n">
@@ -3823,7 +3832,7 @@
       </c>
       <c r="I22" s="7" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>life</t>
         </is>
       </c>
       <c r="J22" s="11" t="n">
@@ -3870,7 +3879,7 @@
       </c>
       <c r="I23" s="8" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>college</t>
         </is>
       </c>
       <c r="J23" s="19" t="n">
@@ -3912,12 +3921,12 @@
       </c>
       <c r="H24" s="7" t="inlineStr">
         <is>
-          <t>Washington D.C.</t>
+          <t>Houston</t>
         </is>
       </c>
       <c r="I24" s="7" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>other</t>
         </is>
       </c>
       <c r="J24" s="7" t="n"/>
@@ -3962,7 +3971,7 @@
       </c>
       <c r="I25" s="8" t="inlineStr">
         <is>
-          <t>referral</t>
+          <t>life</t>
         </is>
       </c>
       <c r="J25" s="19" t="n">
@@ -4004,12 +4013,12 @@
       </c>
       <c r="H26" s="7" t="inlineStr">
         <is>
-          <t>Washington D.C.</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="I26" s="7" t="inlineStr">
         <is>
-          <t>referral</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="J26" s="11" t="n">
@@ -4059,85 +4068,281 @@
           <t>referral</t>
         </is>
       </c>
-      <c r="J27" s="8" t="n"/>
+      <c r="J27" s="19" t="n">
+        <v>46174</v>
+      </c>
       <c r="K27" s="8" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="7" t="n"/>
+      <c r="A28" s="7" t="n">
+        <v>27</v>
+      </c>
       <c r="B28" s="7" t="n"/>
-      <c r="C28" s="7" t="n"/>
-      <c r="D28" s="7" t="n"/>
-      <c r="E28" s="7" t="n"/>
-      <c r="F28" s="14" t="n"/>
-      <c r="G28" s="7" t="n"/>
-      <c r="H28" s="7" t="n"/>
-      <c r="I28" s="7" t="n"/>
-      <c r="J28" s="7" t="n"/>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>Amanda</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>Hanson</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>jenniferdavis@example.com</t>
+        </is>
+      </c>
+      <c r="F28" s="14" t="inlineStr">
+        <is>
+          <t>2179225406</t>
+        </is>
+      </c>
+      <c r="G28" s="7" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/amanda-hanson-1811</t>
+        </is>
+      </c>
+      <c r="H28" s="8" t="inlineStr">
+        <is>
+          <t>Chicago</t>
+        </is>
+      </c>
+      <c r="I28" s="7" t="inlineStr">
+        <is>
+          <t>referral</t>
+        </is>
+      </c>
+      <c r="J28" s="11" t="n">
+        <v>43101</v>
+      </c>
       <c r="K28" s="7" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="7" t="n"/>
+      <c r="A29" s="8" t="n">
+        <v>28</v>
+      </c>
       <c r="B29" s="8" t="n"/>
-      <c r="C29" s="8" t="n"/>
-      <c r="D29" s="8" t="n"/>
-      <c r="E29" s="8" t="n"/>
-      <c r="F29" s="15" t="n"/>
-      <c r="G29" s="8" t="n"/>
-      <c r="H29" s="8" t="n"/>
-      <c r="I29" s="8" t="n"/>
-      <c r="J29" s="8" t="n"/>
+      <c r="C29" s="8" t="inlineStr">
+        <is>
+          <t>Dustin</t>
+        </is>
+      </c>
+      <c r="D29" s="8" t="inlineStr">
+        <is>
+          <t>Freeman</t>
+        </is>
+      </c>
+      <c r="E29" s="8" t="inlineStr">
+        <is>
+          <t>burgessashley@example.org</t>
+        </is>
+      </c>
+      <c r="F29" s="15" t="inlineStr">
+        <is>
+          <t>3652020783</t>
+        </is>
+      </c>
+      <c r="G29" s="8" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/dustin-freeman-7275</t>
+        </is>
+      </c>
+      <c r="H29" s="8" t="inlineStr">
+        <is>
+          <t>New York City</t>
+        </is>
+      </c>
+      <c r="I29" s="7" t="inlineStr">
+        <is>
+          <t>referral</t>
+        </is>
+      </c>
+      <c r="J29" s="11" t="n">
+        <v>43101</v>
+      </c>
       <c r="K29" s="8" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="8" t="n"/>
+      <c r="A30" s="7" t="n">
+        <v>29</v>
+      </c>
       <c r="B30" s="7" t="n"/>
-      <c r="C30" s="7" t="n"/>
-      <c r="D30" s="7" t="n"/>
-      <c r="E30" s="7" t="n"/>
-      <c r="F30" s="14" t="n"/>
-      <c r="G30" s="7" t="n"/>
-      <c r="H30" s="7" t="n"/>
-      <c r="I30" s="7" t="n"/>
-      <c r="J30" s="7" t="n"/>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>Sheri</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>Brown</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>mshea@example.net</t>
+        </is>
+      </c>
+      <c r="F30" s="14" t="inlineStr">
+        <is>
+          <t>5049570007</t>
+        </is>
+      </c>
+      <c r="G30" s="7" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/sheri-brown-0264</t>
+        </is>
+      </c>
+      <c r="H30" s="8" t="inlineStr">
+        <is>
+          <t>Houston</t>
+        </is>
+      </c>
+      <c r="I30" s="7" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="J30" s="11" t="n">
+        <v>43101</v>
+      </c>
       <c r="K30" s="7" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="7" t="n"/>
+      <c r="A31" s="8" t="n">
+        <v>30</v>
+      </c>
       <c r="B31" s="8" t="n"/>
-      <c r="C31" s="8" t="n"/>
-      <c r="D31" s="8" t="n"/>
-      <c r="E31" s="8" t="n"/>
-      <c r="F31" s="15" t="n"/>
-      <c r="G31" s="8" t="n"/>
-      <c r="H31" s="8" t="n"/>
-      <c r="I31" s="8" t="n"/>
-      <c r="J31" s="8" t="n"/>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>Matthew</t>
+        </is>
+      </c>
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t>Sullivan</t>
+        </is>
+      </c>
+      <c r="E31" s="8" t="inlineStr">
+        <is>
+          <t>bentleysusan@example.com</t>
+        </is>
+      </c>
+      <c r="F31" s="15" t="inlineStr">
+        <is>
+          <t>5659674172</t>
+        </is>
+      </c>
+      <c r="G31" s="8" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/matthew-sullivan-7661</t>
+        </is>
+      </c>
+      <c r="H31" s="8" t="inlineStr">
+        <is>
+          <t>Houston</t>
+        </is>
+      </c>
+      <c r="I31" s="7" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="J31" s="11" t="n">
+        <v>43101</v>
+      </c>
       <c r="K31" s="8" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="7" t="n"/>
+      <c r="A32" s="7" t="n">
+        <v>31</v>
+      </c>
       <c r="B32" s="7" t="n"/>
-      <c r="C32" s="7" t="n"/>
-      <c r="D32" s="7" t="n"/>
-      <c r="E32" s="7" t="n"/>
-      <c r="F32" s="14" t="n"/>
-      <c r="G32" s="7" t="n"/>
-      <c r="H32" s="7" t="n"/>
-      <c r="I32" s="7" t="n"/>
-      <c r="J32" s="7" t="n"/>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>David</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>Mcneil</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>zcraig@example.com</t>
+        </is>
+      </c>
+      <c r="F32" s="14" t="inlineStr">
+        <is>
+          <t>3833703459</t>
+        </is>
+      </c>
+      <c r="G32" s="7" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/david-mcneil-7790</t>
+        </is>
+      </c>
+      <c r="H32" s="8" t="inlineStr">
+        <is>
+          <t>Washington D.C.</t>
+        </is>
+      </c>
+      <c r="I32" s="7" t="inlineStr">
+        <is>
+          <t>referral</t>
+        </is>
+      </c>
+      <c r="J32" s="11" t="n">
+        <v>43101</v>
+      </c>
       <c r="K32" s="7" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="8" t="n"/>
-      <c r="B33" s="8" t="n"/>
-      <c r="C33" s="8" t="n"/>
-      <c r="D33" s="8" t="n"/>
-      <c r="E33" s="8" t="n"/>
-      <c r="F33" s="15" t="n"/>
-      <c r="G33" s="8" t="n"/>
-      <c r="H33" s="8" t="n"/>
-      <c r="I33" s="8" t="n"/>
-      <c r="J33" s="8" t="n"/>
+      <c r="A33" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C33" s="8" t="inlineStr">
+        <is>
+          <t>Beverly</t>
+        </is>
+      </c>
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>Gibson</t>
+        </is>
+      </c>
+      <c r="E33" s="8" t="inlineStr">
+        <is>
+          <t>kleincraig@example.org</t>
+        </is>
+      </c>
+      <c r="F33" s="15" t="inlineStr">
+        <is>
+          <t>3294797600</t>
+        </is>
+      </c>
+      <c r="G33" s="8" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/beverly-gibson-1902</t>
+        </is>
+      </c>
+      <c r="H33" s="8" t="inlineStr">
+        <is>
+          <t>Washington D.C.</t>
+        </is>
+      </c>
+      <c r="I33" s="7" t="inlineStr">
+        <is>
+          <t>referral</t>
+        </is>
+      </c>
+      <c r="J33" s="11" t="n">
+        <v>43101</v>
+      </c>
       <c r="K33" s="8" t="n"/>
     </row>
     <row r="34">
@@ -4148,9 +4353,19 @@
       <c r="E34" s="7" t="n"/>
       <c r="F34" s="14" t="n"/>
       <c r="G34" s="7" t="n"/>
-      <c r="H34" s="7" t="n"/>
-      <c r="I34" s="7" t="n"/>
-      <c r="J34" s="7" t="n"/>
+      <c r="H34" s="7" t="inlineStr">
+        <is>
+          <t>Rochester, NY</t>
+        </is>
+      </c>
+      <c r="I34" s="7" t="inlineStr">
+        <is>
+          <t>college</t>
+        </is>
+      </c>
+      <c r="J34" s="11" t="n">
+        <v>43101</v>
+      </c>
       <c r="K34" s="7" t="n"/>
     </row>
     <row r="35">
@@ -6360,15 +6575,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G201"/>
+  <dimension ref="A1:H201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" bestFit="1" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" style="23" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="45" customWidth="1" min="5" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="5" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -6404,439 +6619,488 @@
       </c>
       <c r="G1" s="6" t="inlineStr">
         <is>
+          <t>thank_you_required</t>
+        </is>
+      </c>
+      <c r="H1" s="6" t="inlineStr">
+        <is>
           <t>created_at</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B2" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="C2" s="19" t="n">
+        <v>45879</v>
+      </c>
+      <c r="D2" s="7" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E2" s="8" t="inlineStr">
+        <is>
+          <t>Professional wrong discuss between environment debate.</t>
+        </is>
+      </c>
+      <c r="F2" s="7" t="inlineStr">
+        <is>
+          <t>Tree game friend treat economic improve child trade.</t>
+        </is>
+      </c>
+      <c r="G2" s="17" t="b">
         <v>1</v>
       </c>
-      <c r="B2" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="C2" s="11" t="n">
-        <v>45991</v>
-      </c>
-      <c r="D2" s="7" t="inlineStr">
-        <is>
-          <t>in person</t>
-        </is>
-      </c>
-      <c r="E2" s="17" t="inlineStr">
-        <is>
-          <t>As majority those decide bad answer group.</t>
-        </is>
-      </c>
-      <c r="F2" s="17" t="inlineStr">
-        <is>
-          <t>Return life raise improve.</t>
-        </is>
-      </c>
-      <c r="G2" s="7" t="n"/>
+      <c r="H2" s="8" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="C3" s="19" t="n">
-        <v>46120</v>
+        <v>9</v>
+      </c>
+      <c r="B3" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="C3" s="11" t="n">
+        <v>45842</v>
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="E3" s="8" t="inlineStr">
-        <is>
-          <t>Computer fill property down get.</t>
-        </is>
-      </c>
-      <c r="F3" s="8" t="inlineStr">
-        <is>
-          <t>Important central cut cause get audience.</t>
-        </is>
-      </c>
-      <c r="G3" s="8" t="n"/>
+          <t>thank you</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>Thought myself usually.</t>
+        </is>
+      </c>
+      <c r="F3" s="7" t="n"/>
+      <c r="G3" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="H3" s="7" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="n">
-        <v>3</v>
+      <c r="A4" s="8" t="n">
+        <v>7</v>
       </c>
       <c r="B4" s="7" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C4" s="11" t="n">
-        <v>46128</v>
+        <v>45898</v>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
+          <t>in person</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>Someone there between laugh event allow middle finish.</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>Two within director beautiful page.</t>
+        </is>
+      </c>
+      <c r="G4" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="H4" s="7" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="B5" s="8" t="n">
+        <v>23</v>
+      </c>
+      <c r="C5" s="19" t="n">
+        <v>46073</v>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>in person</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>Hold mouth generation teacher wide attorney own.</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>Describe adult final or low make.</t>
+        </is>
+      </c>
+      <c r="G5" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="H5" s="8" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="n">
+        <v>22</v>
+      </c>
+      <c r="B6" s="8" t="n">
+        <v>23</v>
+      </c>
+      <c r="C6" s="27" t="n">
+        <v>45959</v>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
           <t>thank you</t>
         </is>
       </c>
-      <c r="E4" s="7" t="inlineStr">
-        <is>
-          <t>Side foot home show threat recently audience.</t>
-        </is>
-      </c>
-      <c r="F4" s="7" t="inlineStr">
-        <is>
-          <t>Enter exist close there natural east appear.</t>
-        </is>
-      </c>
-      <c r="G4" s="7" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="C5" s="11" t="n">
-        <v>45834</v>
-      </c>
-      <c r="D5" s="7" t="inlineStr">
-        <is>
-          <t>thank you</t>
-        </is>
-      </c>
-      <c r="E5" s="8" t="inlineStr">
-        <is>
-          <t>Air nature name yes factor accept where.</t>
-        </is>
-      </c>
-      <c r="F5" s="8" t="n"/>
-      <c r="G5" s="8" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="C6" s="23" t="n">
-        <v>45862</v>
-      </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>thank you</t>
-        </is>
-      </c>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>Heart down store technology.</t>
-        </is>
-      </c>
-      <c r="F6" s="7" t="inlineStr">
-        <is>
-          <t>Almost after particularly.</t>
-        </is>
-      </c>
-      <c r="G6" s="7" t="n"/>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>Whole result analysis end minute.</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="n"/>
+      <c r="G6" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="H6" s="8" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="24" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="B7" s="25" t="n">
+        <v>10</v>
       </c>
       <c r="C7" s="19" t="n">
-        <v>45729</v>
+        <v>45900</v>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>call</t>
-        </is>
-      </c>
-      <c r="E7" s="8" t="inlineStr">
-        <is>
-          <t>Spring in interview one fine matter.</t>
-        </is>
-      </c>
-      <c r="F7" s="7" t="inlineStr">
-        <is>
-          <t>Detail project control unit around mean notice name.</t>
-        </is>
-      </c>
-      <c r="G7" s="8" t="n"/>
+          <t>thank you</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>Probably protect type we student community general.</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="n"/>
+      <c r="G7" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="H7" s="8" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="n">
-        <v>7</v>
+      <c r="A8" s="7" t="n">
+        <v>15</v>
       </c>
       <c r="B8" s="7" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>45794</v>
+        <v>46268</v>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>Cell color knowledge local democratic center PM.</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>Them line serve over yard indicate.</t>
+        </is>
+      </c>
+      <c r="G8" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="H8" s="7" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B9" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="C9" s="19" t="n">
+        <v>46298</v>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>Break like week six maybe seat with.</t>
-        </is>
-      </c>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t>Similar believe Republican know her involve first clear.</t>
-        </is>
-      </c>
-      <c r="G8" s="7" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="C9" s="19" t="n">
-        <v>46102</v>
-      </c>
-      <c r="D9" s="7" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>Me after middle deep scientist.</t>
+          <t>Enjoy place possible.</t>
         </is>
       </c>
       <c r="F9" s="8" t="inlineStr">
         <is>
-          <t>Rate up painting save popular other along matter.</t>
-        </is>
-      </c>
-      <c r="G9" s="8" t="n"/>
+          <t>Watch throw former bar fact.</t>
+        </is>
+      </c>
+      <c r="G9" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="H9" s="8" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="C10" s="11" t="n">
-        <v>46153</v>
+      <c r="A10" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="B10" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="C10" s="19" t="n">
+        <v>46164</v>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="E10" s="7" t="inlineStr">
-        <is>
-          <t>Inside mouth home himself.</t>
-        </is>
-      </c>
-      <c r="F10" s="7" t="n"/>
-      <c r="G10" s="7" t="n"/>
+          <t>in person</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>Expect computer son local network economic their.</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="inlineStr">
+        <is>
+          <t>Another company her as let coach.</t>
+        </is>
+      </c>
+      <c r="G10" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="H10" s="8" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B11" s="8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C11" s="19" t="n">
-        <v>46235</v>
+        <v>46189</v>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>call</t>
-        </is>
-      </c>
-      <c r="E11" s="7" t="inlineStr">
-        <is>
-          <t>Different three serve read.</t>
-        </is>
-      </c>
-      <c r="F11" s="8" t="n"/>
-      <c r="G11" s="8" t="n"/>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>Prevent yes position interesting fact ok.</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="inlineStr">
+        <is>
+          <t>As town small conference PM white.</t>
+        </is>
+      </c>
+      <c r="G11" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="H11" s="8" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" s="7" t="n">
-        <v>11</v>
-      </c>
-      <c r="C12" s="11" t="n">
-        <v>46104</v>
+        <v>18</v>
+      </c>
+      <c r="B12" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="C12" s="19" t="n">
+        <v>45848</v>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
           <t>call</t>
         </is>
       </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>Somebody keep seek defense.</t>
-        </is>
-      </c>
-      <c r="F12" s="7" t="inlineStr">
-        <is>
-          <t>Test morning structure.</t>
-        </is>
-      </c>
-      <c r="G12" s="7" t="n"/>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>Find write another garden difference team hold.</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t>Financial full better hotel.</t>
+        </is>
+      </c>
+      <c r="G12" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="H12" s="8" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" s="8" t="n">
-        <v>12</v>
+      <c r="A13" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="B13" s="7" t="n">
+        <v>3</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>45666</v>
+        <v>46012</v>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>thank you</t>
-        </is>
-      </c>
-      <c r="E13" s="7" t="inlineStr">
-        <is>
-          <t>Word space head case after last apply.</t>
-        </is>
-      </c>
-      <c r="F13" s="7" t="inlineStr">
-        <is>
-          <t>Ok design fire.</t>
-        </is>
-      </c>
-      <c r="G13" s="8" t="n"/>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="E13" s="17" t="inlineStr">
+        <is>
+          <t>Every tonight point friend support onto near.</t>
+        </is>
+      </c>
+      <c r="F13" s="17" t="inlineStr">
+        <is>
+          <t>Easy wide two against measure space.</t>
+        </is>
+      </c>
+      <c r="G13" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="H13" s="7" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="B14" s="7" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C14" s="11" t="n">
-        <v>45689</v>
+        <v>46149</v>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>in person</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>Three occur painting.</t>
+          <t>Rate service by laugh window environment.</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
-          <t>Candidate center story guess white tend here.</t>
-        </is>
-      </c>
-      <c r="G14" s="7" t="n"/>
+          <t>Question help would indeed.</t>
+        </is>
+      </c>
+      <c r="G14" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="H14" s="7" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="8" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" s="8" t="n">
-        <v>17</v>
+        <v>4</v>
+      </c>
+      <c r="B15" s="7" t="n">
+        <v>7</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>45964</v>
+        <v>46124</v>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="E15" s="7" t="inlineStr">
-        <is>
-          <t>Out want world arrive suggest.</t>
-        </is>
-      </c>
-      <c r="F15" s="7" t="inlineStr">
-        <is>
-          <t>Far agent right policy enter.</t>
-        </is>
-      </c>
-      <c r="G15" s="8" t="n"/>
+          <t>thank you</t>
+        </is>
+      </c>
+      <c r="E15" s="8" t="inlineStr">
+        <is>
+          <t>For small for design.</t>
+        </is>
+      </c>
+      <c r="F15" s="8" t="n"/>
+      <c r="G15" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="H15" s="8" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="B16" s="7" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="C16" s="11" t="n">
-        <v>45767</v>
+        <v>46079</v>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>other</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>Significant race reduce market.</t>
+          <t>Share generation cell one available explain church.</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
-          <t>Pick former same various call fight.</t>
-        </is>
-      </c>
-      <c r="G16" s="7" t="n"/>
+          <t>Foreign rate include fly soon.</t>
+        </is>
+      </c>
+      <c r="G16" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="H16" s="7" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" s="8" t="n">
-        <v>13</v>
-      </c>
-      <c r="C17" s="19" t="n">
-        <v>45879</v>
+        <v>11</v>
+      </c>
+      <c r="B17" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="C17" s="11" t="n">
+        <v>46340</v>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="E17" s="8" t="inlineStr">
-        <is>
-          <t>Professional wrong discuss between environment debate.</t>
-        </is>
-      </c>
-      <c r="F17" s="8" t="inlineStr">
-        <is>
-          <t>Tree game friend treat economic improve child trade.</t>
-        </is>
-      </c>
-      <c r="G17" s="8" t="n"/>
+          <t>in person</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>Tree lose rock who mother listen dream.</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>Picture prove serious low.</t>
+        </is>
+      </c>
+      <c r="G17" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="H17" s="7" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="8" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" s="7" t="n">
-        <v>13</v>
+        <v>12</v>
+      </c>
+      <c r="B18" s="8" t="n">
+        <v>12</v>
       </c>
       <c r="C18" s="11" t="n">
-        <v>45842</v>
+        <v>45716</v>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
@@ -6845,106 +7109,118 @@
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>Thought myself usually.</t>
+          <t>Anyone their soldier fish hospital case.</t>
         </is>
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
-          <t>Someone there between laugh event allow middle finish.</t>
-        </is>
-      </c>
-      <c r="G18" s="7" t="n"/>
+          <t>Play represent leg else behind hit action.</t>
+        </is>
+      </c>
+      <c r="G18" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="H18" s="8" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="C19" s="19" t="n">
-        <v>46349</v>
+        <v>13</v>
+      </c>
+      <c r="B19" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="C19" s="11" t="n">
+        <v>46126</v>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
           <t>call</t>
         </is>
       </c>
-      <c r="E19" s="8" t="inlineStr">
-        <is>
-          <t>Suffer game short town two.</t>
-        </is>
-      </c>
-      <c r="F19" s="8" t="inlineStr">
-        <is>
-          <t>Beautiful page newspaper read of wrong run.</t>
-        </is>
-      </c>
-      <c r="G19" s="8" t="n"/>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>Which only once thus candidate play top.</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>Reality student simply still building.</t>
+        </is>
+      </c>
+      <c r="G19" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="H19" s="7" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="8" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" s="7" t="n">
-        <v>21</v>
+        <v>14</v>
+      </c>
+      <c r="B20" s="8" t="n">
+        <v>17</v>
       </c>
       <c r="C20" s="11" t="n">
-        <v>45828</v>
+        <v>45800</v>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>thank you</t>
+          <t>in person</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>Attorney own movement history degree build.</t>
+          <t>General yeah seven morning say second.</t>
         </is>
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
-          <t>Low make window whole result analysis.</t>
-        </is>
-      </c>
-      <c r="G20" s="7" t="n"/>
+          <t>Garden color mouth present.</t>
+        </is>
+      </c>
+      <c r="G20" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="H20" s="8" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="7" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" s="8" t="n">
-        <v>23</v>
-      </c>
-      <c r="C21" s="19" t="n">
-        <v>46375</v>
+      <c r="A21" s="8" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="C21" s="11" t="n">
+        <v>45970</v>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="E21" s="8" t="inlineStr">
-        <is>
-          <t>Little walk several probably protect.</t>
-        </is>
-      </c>
-      <c r="F21" s="8" t="inlineStr">
-        <is>
-          <t>Can instead method even.</t>
-        </is>
-      </c>
-      <c r="G21" s="8" t="n"/>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>Prevent weight tell various.</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>Friend fall at my.</t>
+        </is>
+      </c>
+      <c r="G21" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="H21" s="7" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" s="7" t="n">
-        <v>23</v>
-      </c>
-      <c r="C22" s="11" t="n">
-        <v>46024</v>
+        <v>5</v>
+      </c>
+      <c r="B22" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="C22" s="26" t="n">
+        <v>46149</v>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
@@ -6953,38 +7229,48 @@
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>Suggest happen size scene simple peace them.</t>
+          <t>Would improve pattern candidate to.</t>
         </is>
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
-          <t>From system recognize enjoy place possible station senior.</t>
-        </is>
-      </c>
-      <c r="G22" s="7" t="n"/>
+          <t>Point picture happy recently likely.</t>
+        </is>
+      </c>
+      <c r="G22" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="H22" s="7" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="8" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" s="8" t="n">
-        <v>23</v>
-      </c>
-      <c r="C23" s="19" t="n">
-        <v>46170</v>
+        <v>19</v>
+      </c>
+      <c r="B23" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="C23" s="11" t="n">
+        <v>46043</v>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>in person</t>
-        </is>
-      </c>
-      <c r="E23" s="8" t="inlineStr">
-        <is>
-          <t>Throw former bar fact mind in.</t>
-        </is>
-      </c>
-      <c r="F23" s="8" t="n"/>
-      <c r="G23" s="8" t="n"/>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>Nation clearly bring him move popular.</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>Fact skill answer own ball.</t>
+        </is>
+      </c>
+      <c r="G23" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="H23" s="7" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
@@ -6994,20 +7280,23 @@
         <v>25</v>
       </c>
       <c r="C24" s="11" t="n">
-        <v>45886</v>
+        <v>45932</v>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>email</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>Appear form lot none glass guy city.</t>
+          <t>Himself serious note cost rule.</t>
         </is>
       </c>
       <c r="F24" s="7" t="n"/>
-      <c r="G24" s="7" t="n"/>
+      <c r="G24" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="H24" s="7" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="8" t="n">
@@ -7017,7 +7306,7 @@
         <v>24</v>
       </c>
       <c r="C25" s="19" t="n">
-        <v>46378</v>
+        <v>45742</v>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
@@ -7026,11 +7315,14 @@
       </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t>Task rise arrive prevent.</t>
+          <t>Become similar than federal.</t>
         </is>
       </c>
       <c r="F25" s="8" t="n"/>
-      <c r="G25" s="8" t="n"/>
+      <c r="G25" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="H25" s="8" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
@@ -7040,7 +7332,7 @@
         <v>2</v>
       </c>
       <c r="C26" s="11" t="n">
-        <v>45961</v>
+        <v>45876</v>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
@@ -7049,15 +7341,18 @@
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>Doctor mission exactly me just drive.</t>
+          <t>Fire add that nature.</t>
         </is>
       </c>
       <c r="F26" s="7" t="inlineStr">
         <is>
-          <t>Visit suggest statement find.</t>
-        </is>
-      </c>
-      <c r="G26" s="7" t="n"/>
+          <t>Woman require whole drug finally impact plan.</t>
+        </is>
+      </c>
+      <c r="G26" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="H26" s="7" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="8" t="n">
@@ -7067,24 +7362,27 @@
         <v>24</v>
       </c>
       <c r="C27" s="19" t="n">
-        <v>46255</v>
+        <v>45878</v>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>email</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr">
         <is>
-          <t>Song dinner agree.</t>
+          <t>Treatment include nature group never.</t>
         </is>
       </c>
       <c r="F27" s="8" t="inlineStr">
         <is>
-          <t>Water color game name you.</t>
-        </is>
-      </c>
-      <c r="G27" s="8" t="n"/>
+          <t>Language then who commercial scientist special science.</t>
+        </is>
+      </c>
+      <c r="G27" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="H27" s="8" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
@@ -7094,38 +7392,83 @@
         <v>24</v>
       </c>
       <c r="C28" s="19" t="n">
-        <v>46012</v>
+        <v>46106</v>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>thank you</t>
         </is>
       </c>
       <c r="E28" s="8" t="inlineStr">
         <is>
-          <t>Every tonight point friend support onto near.</t>
+          <t>Result throughout always answer.</t>
         </is>
       </c>
       <c r="F28" s="8" t="n"/>
-      <c r="G28" s="7" t="n"/>
+      <c r="G28" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="H28" s="7" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="8" t="n"/>
-      <c r="B29" s="8" t="n"/>
-      <c r="C29" s="19" t="n"/>
-      <c r="D29" s="8" t="n"/>
-      <c r="E29" s="8" t="n"/>
-      <c r="F29" s="8" t="n"/>
-      <c r="G29" s="8" t="n"/>
+      <c r="A29" s="8" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="C29" s="19" t="n">
+        <v>45978</v>
+      </c>
+      <c r="D29" s="8" t="inlineStr">
+        <is>
+          <t>call</t>
+        </is>
+      </c>
+      <c r="E29" s="8" t="inlineStr">
+        <is>
+          <t>Range theory news read.</t>
+        </is>
+      </c>
+      <c r="F29" s="8" t="inlineStr">
+        <is>
+          <t>Play improve board area just hot.</t>
+        </is>
+      </c>
+      <c r="G29" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="H29" s="8" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="7" t="n"/>
-      <c r="B30" s="7" t="n"/>
-      <c r="C30" s="11" t="n"/>
-      <c r="D30" s="7" t="n"/>
-      <c r="E30" s="7" t="n"/>
-      <c r="F30" s="7" t="n"/>
-      <c r="G30" s="7" t="n"/>
+      <c r="A30" s="7" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="7" t="n">
+        <v>26</v>
+      </c>
+      <c r="C30" s="11" t="n">
+        <v>46048</v>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>thank you</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>Century record until center.</t>
+        </is>
+      </c>
+      <c r="F30" s="7" t="inlineStr">
+        <is>
+          <t>Bag industry finish community indicate picture rule benefit.</t>
+        </is>
+      </c>
+      <c r="G30" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="H30" s="7" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="8" t="n"/>
@@ -7135,6 +7478,7 @@
       <c r="E31" s="8" t="n"/>
       <c r="F31" s="8" t="n"/>
       <c r="G31" s="8" t="n"/>
+      <c r="H31" s="8" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="7" t="n"/>
@@ -7144,6 +7488,7 @@
       <c r="E32" s="7" t="n"/>
       <c r="F32" s="7" t="n"/>
       <c r="G32" s="7" t="n"/>
+      <c r="H32" s="7" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="8" t="n"/>
@@ -7153,6 +7498,7 @@
       <c r="E33" s="8" t="n"/>
       <c r="F33" s="8" t="n"/>
       <c r="G33" s="8" t="n"/>
+      <c r="H33" s="8" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="7" t="n"/>
@@ -7162,6 +7508,7 @@
       <c r="E34" s="7" t="n"/>
       <c r="F34" s="7" t="n"/>
       <c r="G34" s="7" t="n"/>
+      <c r="H34" s="7" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="8" t="n"/>
@@ -7171,6 +7518,7 @@
       <c r="E35" s="8" t="n"/>
       <c r="F35" s="8" t="n"/>
       <c r="G35" s="8" t="n"/>
+      <c r="H35" s="8" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="7" t="n"/>
@@ -7180,6 +7528,7 @@
       <c r="E36" s="7" t="n"/>
       <c r="F36" s="7" t="n"/>
       <c r="G36" s="7" t="n"/>
+      <c r="H36" s="7" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="8" t="n"/>
@@ -7189,6 +7538,7 @@
       <c r="E37" s="8" t="n"/>
       <c r="F37" s="8" t="n"/>
       <c r="G37" s="8" t="n"/>
+      <c r="H37" s="8" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="7" t="n"/>
@@ -7198,6 +7548,7 @@
       <c r="E38" s="7" t="n"/>
       <c r="F38" s="7" t="n"/>
       <c r="G38" s="7" t="n"/>
+      <c r="H38" s="7" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="8" t="n"/>
@@ -7207,6 +7558,7 @@
       <c r="E39" s="8" t="n"/>
       <c r="F39" s="8" t="n"/>
       <c r="G39" s="8" t="n"/>
+      <c r="H39" s="8" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="7" t="n"/>
@@ -7216,6 +7568,7 @@
       <c r="E40" s="7" t="n"/>
       <c r="F40" s="7" t="n"/>
       <c r="G40" s="7" t="n"/>
+      <c r="H40" s="7" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="8" t="n"/>
@@ -7225,6 +7578,7 @@
       <c r="E41" s="8" t="n"/>
       <c r="F41" s="8" t="n"/>
       <c r="G41" s="8" t="n"/>
+      <c r="H41" s="8" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="7" t="n"/>
@@ -7234,6 +7588,7 @@
       <c r="E42" s="7" t="n"/>
       <c r="F42" s="7" t="n"/>
       <c r="G42" s="7" t="n"/>
+      <c r="H42" s="7" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="8" t="n"/>
@@ -7243,6 +7598,7 @@
       <c r="E43" s="8" t="n"/>
       <c r="F43" s="8" t="n"/>
       <c r="G43" s="8" t="n"/>
+      <c r="H43" s="8" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="7" t="n"/>
@@ -7252,6 +7608,7 @@
       <c r="E44" s="7" t="n"/>
       <c r="F44" s="7" t="n"/>
       <c r="G44" s="7" t="n"/>
+      <c r="H44" s="7" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="8" t="n"/>
@@ -7261,6 +7618,7 @@
       <c r="E45" s="8" t="n"/>
       <c r="F45" s="8" t="n"/>
       <c r="G45" s="8" t="n"/>
+      <c r="H45" s="8" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="7" t="n"/>
@@ -7270,6 +7628,7 @@
       <c r="E46" s="7" t="n"/>
       <c r="F46" s="7" t="n"/>
       <c r="G46" s="7" t="n"/>
+      <c r="H46" s="7" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="8" t="n"/>
@@ -7279,6 +7638,7 @@
       <c r="E47" s="8" t="n"/>
       <c r="F47" s="8" t="n"/>
       <c r="G47" s="8" t="n"/>
+      <c r="H47" s="8" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="7" t="n"/>
@@ -7288,6 +7648,7 @@
       <c r="E48" s="7" t="n"/>
       <c r="F48" s="7" t="n"/>
       <c r="G48" s="7" t="n"/>
+      <c r="H48" s="7" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="8" t="n"/>
@@ -7297,6 +7658,7 @@
       <c r="E49" s="8" t="n"/>
       <c r="F49" s="8" t="n"/>
       <c r="G49" s="8" t="n"/>
+      <c r="H49" s="8" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="7" t="n"/>
@@ -7306,6 +7668,7 @@
       <c r="E50" s="7" t="n"/>
       <c r="F50" s="7" t="n"/>
       <c r="G50" s="7" t="n"/>
+      <c r="H50" s="7" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="8" t="n"/>
@@ -7315,6 +7678,7 @@
       <c r="E51" s="8" t="n"/>
       <c r="F51" s="8" t="n"/>
       <c r="G51" s="8" t="n"/>
+      <c r="H51" s="8" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="7" t="n"/>
@@ -7324,6 +7688,7 @@
       <c r="E52" s="7" t="n"/>
       <c r="F52" s="7" t="n"/>
       <c r="G52" s="7" t="n"/>
+      <c r="H52" s="7" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="8" t="n"/>
@@ -7333,6 +7698,7 @@
       <c r="E53" s="8" t="n"/>
       <c r="F53" s="8" t="n"/>
       <c r="G53" s="8" t="n"/>
+      <c r="H53" s="8" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="7" t="n"/>
@@ -7342,6 +7708,7 @@
       <c r="E54" s="7" t="n"/>
       <c r="F54" s="7" t="n"/>
       <c r="G54" s="7" t="n"/>
+      <c r="H54" s="7" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="8" t="n"/>
@@ -7351,6 +7718,7 @@
       <c r="E55" s="8" t="n"/>
       <c r="F55" s="8" t="n"/>
       <c r="G55" s="8" t="n"/>
+      <c r="H55" s="8" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="7" t="n"/>
@@ -7360,6 +7728,7 @@
       <c r="E56" s="7" t="n"/>
       <c r="F56" s="7" t="n"/>
       <c r="G56" s="7" t="n"/>
+      <c r="H56" s="7" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="8" t="n"/>
@@ -7369,6 +7738,7 @@
       <c r="E57" s="8" t="n"/>
       <c r="F57" s="8" t="n"/>
       <c r="G57" s="8" t="n"/>
+      <c r="H57" s="8" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="7" t="n"/>
@@ -7378,6 +7748,7 @@
       <c r="E58" s="7" t="n"/>
       <c r="F58" s="7" t="n"/>
       <c r="G58" s="7" t="n"/>
+      <c r="H58" s="7" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="8" t="n"/>
@@ -7387,6 +7758,7 @@
       <c r="E59" s="8" t="n"/>
       <c r="F59" s="8" t="n"/>
       <c r="G59" s="8" t="n"/>
+      <c r="H59" s="8" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="7" t="n"/>
@@ -7396,6 +7768,7 @@
       <c r="E60" s="7" t="n"/>
       <c r="F60" s="7" t="n"/>
       <c r="G60" s="7" t="n"/>
+      <c r="H60" s="7" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="8" t="n"/>
@@ -7405,6 +7778,7 @@
       <c r="E61" s="8" t="n"/>
       <c r="F61" s="8" t="n"/>
       <c r="G61" s="8" t="n"/>
+      <c r="H61" s="8" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="7" t="n"/>
@@ -7414,6 +7788,7 @@
       <c r="E62" s="7" t="n"/>
       <c r="F62" s="7" t="n"/>
       <c r="G62" s="7" t="n"/>
+      <c r="H62" s="7" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="8" t="n"/>
@@ -7423,6 +7798,7 @@
       <c r="E63" s="8" t="n"/>
       <c r="F63" s="8" t="n"/>
       <c r="G63" s="8" t="n"/>
+      <c r="H63" s="8" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="7" t="n"/>
@@ -7432,6 +7808,7 @@
       <c r="E64" s="7" t="n"/>
       <c r="F64" s="7" t="n"/>
       <c r="G64" s="7" t="n"/>
+      <c r="H64" s="7" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="8" t="n"/>
@@ -7441,6 +7818,7 @@
       <c r="E65" s="8" t="n"/>
       <c r="F65" s="8" t="n"/>
       <c r="G65" s="8" t="n"/>
+      <c r="H65" s="8" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="7" t="n"/>
@@ -7450,6 +7828,7 @@
       <c r="E66" s="7" t="n"/>
       <c r="F66" s="7" t="n"/>
       <c r="G66" s="7" t="n"/>
+      <c r="H66" s="7" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="8" t="n"/>
@@ -7459,6 +7838,7 @@
       <c r="E67" s="8" t="n"/>
       <c r="F67" s="8" t="n"/>
       <c r="G67" s="8" t="n"/>
+      <c r="H67" s="8" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="7" t="n"/>
@@ -7468,6 +7848,7 @@
       <c r="E68" s="7" t="n"/>
       <c r="F68" s="7" t="n"/>
       <c r="G68" s="7" t="n"/>
+      <c r="H68" s="7" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="8" t="n"/>
@@ -7477,6 +7858,7 @@
       <c r="E69" s="8" t="n"/>
       <c r="F69" s="8" t="n"/>
       <c r="G69" s="8" t="n"/>
+      <c r="H69" s="8" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="7" t="n"/>
@@ -7486,6 +7868,7 @@
       <c r="E70" s="7" t="n"/>
       <c r="F70" s="7" t="n"/>
       <c r="G70" s="7" t="n"/>
+      <c r="H70" s="7" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="8" t="n"/>
@@ -7495,6 +7878,7 @@
       <c r="E71" s="8" t="n"/>
       <c r="F71" s="8" t="n"/>
       <c r="G71" s="8" t="n"/>
+      <c r="H71" s="8" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="7" t="n"/>
@@ -7504,6 +7888,7 @@
       <c r="E72" s="7" t="n"/>
       <c r="F72" s="7" t="n"/>
       <c r="G72" s="7" t="n"/>
+      <c r="H72" s="7" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="8" t="n"/>
@@ -7513,6 +7898,7 @@
       <c r="E73" s="8" t="n"/>
       <c r="F73" s="8" t="n"/>
       <c r="G73" s="8" t="n"/>
+      <c r="H73" s="8" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="7" t="n"/>
@@ -7522,6 +7908,7 @@
       <c r="E74" s="7" t="n"/>
       <c r="F74" s="7" t="n"/>
       <c r="G74" s="7" t="n"/>
+      <c r="H74" s="7" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="8" t="n"/>
@@ -7531,6 +7918,7 @@
       <c r="E75" s="8" t="n"/>
       <c r="F75" s="8" t="n"/>
       <c r="G75" s="8" t="n"/>
+      <c r="H75" s="8" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="7" t="n"/>
@@ -7540,6 +7928,7 @@
       <c r="E76" s="7" t="n"/>
       <c r="F76" s="7" t="n"/>
       <c r="G76" s="7" t="n"/>
+      <c r="H76" s="7" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="8" t="n"/>
@@ -7549,6 +7938,7 @@
       <c r="E77" s="8" t="n"/>
       <c r="F77" s="8" t="n"/>
       <c r="G77" s="8" t="n"/>
+      <c r="H77" s="8" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="7" t="n"/>
@@ -7558,6 +7948,7 @@
       <c r="E78" s="7" t="n"/>
       <c r="F78" s="7" t="n"/>
       <c r="G78" s="7" t="n"/>
+      <c r="H78" s="7" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="8" t="n"/>
@@ -7567,6 +7958,7 @@
       <c r="E79" s="8" t="n"/>
       <c r="F79" s="8" t="n"/>
       <c r="G79" s="8" t="n"/>
+      <c r="H79" s="8" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="7" t="n"/>
@@ -7576,6 +7968,7 @@
       <c r="E80" s="7" t="n"/>
       <c r="F80" s="7" t="n"/>
       <c r="G80" s="7" t="n"/>
+      <c r="H80" s="7" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="8" t="n"/>
@@ -7585,6 +7978,7 @@
       <c r="E81" s="8" t="n"/>
       <c r="F81" s="8" t="n"/>
       <c r="G81" s="8" t="n"/>
+      <c r="H81" s="8" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="7" t="n"/>
@@ -7594,6 +7988,7 @@
       <c r="E82" s="7" t="n"/>
       <c r="F82" s="7" t="n"/>
       <c r="G82" s="7" t="n"/>
+      <c r="H82" s="7" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="8" t="n"/>
@@ -7603,6 +7998,7 @@
       <c r="E83" s="8" t="n"/>
       <c r="F83" s="8" t="n"/>
       <c r="G83" s="8" t="n"/>
+      <c r="H83" s="8" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="7" t="n"/>
@@ -7612,6 +8008,7 @@
       <c r="E84" s="7" t="n"/>
       <c r="F84" s="7" t="n"/>
       <c r="G84" s="7" t="n"/>
+      <c r="H84" s="7" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="8" t="n"/>
@@ -7621,6 +8018,7 @@
       <c r="E85" s="8" t="n"/>
       <c r="F85" s="8" t="n"/>
       <c r="G85" s="8" t="n"/>
+      <c r="H85" s="8" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="7" t="n"/>
@@ -7630,6 +8028,7 @@
       <c r="E86" s="7" t="n"/>
       <c r="F86" s="7" t="n"/>
       <c r="G86" s="7" t="n"/>
+      <c r="H86" s="7" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="8" t="n"/>
@@ -7639,6 +8038,7 @@
       <c r="E87" s="8" t="n"/>
       <c r="F87" s="8" t="n"/>
       <c r="G87" s="8" t="n"/>
+      <c r="H87" s="8" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="7" t="n"/>
@@ -7648,6 +8048,7 @@
       <c r="E88" s="7" t="n"/>
       <c r="F88" s="7" t="n"/>
       <c r="G88" s="7" t="n"/>
+      <c r="H88" s="7" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="8" t="n"/>
@@ -7657,6 +8058,7 @@
       <c r="E89" s="8" t="n"/>
       <c r="F89" s="8" t="n"/>
       <c r="G89" s="8" t="n"/>
+      <c r="H89" s="8" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="7" t="n"/>
@@ -7666,6 +8068,7 @@
       <c r="E90" s="7" t="n"/>
       <c r="F90" s="7" t="n"/>
       <c r="G90" s="7" t="n"/>
+      <c r="H90" s="7" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="8" t="n"/>
@@ -7675,6 +8078,7 @@
       <c r="E91" s="8" t="n"/>
       <c r="F91" s="8" t="n"/>
       <c r="G91" s="8" t="n"/>
+      <c r="H91" s="8" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="7" t="n"/>
@@ -7684,6 +8088,7 @@
       <c r="E92" s="7" t="n"/>
       <c r="F92" s="7" t="n"/>
       <c r="G92" s="7" t="n"/>
+      <c r="H92" s="7" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="8" t="n"/>
@@ -7693,6 +8098,7 @@
       <c r="E93" s="8" t="n"/>
       <c r="F93" s="8" t="n"/>
       <c r="G93" s="8" t="n"/>
+      <c r="H93" s="8" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="7" t="n"/>
@@ -7702,6 +8108,7 @@
       <c r="E94" s="7" t="n"/>
       <c r="F94" s="7" t="n"/>
       <c r="G94" s="7" t="n"/>
+      <c r="H94" s="7" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="8" t="n"/>
@@ -7711,6 +8118,7 @@
       <c r="E95" s="8" t="n"/>
       <c r="F95" s="8" t="n"/>
       <c r="G95" s="8" t="n"/>
+      <c r="H95" s="8" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="7" t="n"/>
@@ -7720,6 +8128,7 @@
       <c r="E96" s="7" t="n"/>
       <c r="F96" s="7" t="n"/>
       <c r="G96" s="7" t="n"/>
+      <c r="H96" s="7" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="8" t="n"/>
@@ -7729,6 +8138,7 @@
       <c r="E97" s="8" t="n"/>
       <c r="F97" s="8" t="n"/>
       <c r="G97" s="8" t="n"/>
+      <c r="H97" s="8" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="7" t="n"/>
@@ -7738,6 +8148,7 @@
       <c r="E98" s="7" t="n"/>
       <c r="F98" s="7" t="n"/>
       <c r="G98" s="7" t="n"/>
+      <c r="H98" s="7" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="8" t="n"/>
@@ -7747,6 +8158,7 @@
       <c r="E99" s="8" t="n"/>
       <c r="F99" s="8" t="n"/>
       <c r="G99" s="8" t="n"/>
+      <c r="H99" s="8" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="7" t="n"/>
@@ -7756,6 +8168,7 @@
       <c r="E100" s="7" t="n"/>
       <c r="F100" s="7" t="n"/>
       <c r="G100" s="7" t="n"/>
+      <c r="H100" s="7" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="8" t="n"/>
@@ -7765,6 +8178,7 @@
       <c r="E101" s="8" t="n"/>
       <c r="F101" s="8" t="n"/>
       <c r="G101" s="8" t="n"/>
+      <c r="H101" s="8" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="7" t="n"/>
@@ -7774,6 +8188,7 @@
       <c r="E102" s="7" t="n"/>
       <c r="F102" s="7" t="n"/>
       <c r="G102" s="7" t="n"/>
+      <c r="H102" s="7" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="8" t="n"/>
@@ -7783,6 +8198,7 @@
       <c r="E103" s="8" t="n"/>
       <c r="F103" s="8" t="n"/>
       <c r="G103" s="8" t="n"/>
+      <c r="H103" s="8" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="7" t="n"/>
@@ -7792,6 +8208,7 @@
       <c r="E104" s="7" t="n"/>
       <c r="F104" s="7" t="n"/>
       <c r="G104" s="7" t="n"/>
+      <c r="H104" s="7" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="8" t="n"/>
@@ -7801,6 +8218,7 @@
       <c r="E105" s="8" t="n"/>
       <c r="F105" s="8" t="n"/>
       <c r="G105" s="8" t="n"/>
+      <c r="H105" s="8" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="7" t="n"/>
@@ -7810,6 +8228,7 @@
       <c r="E106" s="7" t="n"/>
       <c r="F106" s="7" t="n"/>
       <c r="G106" s="7" t="n"/>
+      <c r="H106" s="7" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="8" t="n"/>
@@ -7819,6 +8238,7 @@
       <c r="E107" s="8" t="n"/>
       <c r="F107" s="8" t="n"/>
       <c r="G107" s="8" t="n"/>
+      <c r="H107" s="8" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="7" t="n"/>
@@ -7828,6 +8248,7 @@
       <c r="E108" s="7" t="n"/>
       <c r="F108" s="7" t="n"/>
       <c r="G108" s="7" t="n"/>
+      <c r="H108" s="7" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="8" t="n"/>
@@ -7837,6 +8258,7 @@
       <c r="E109" s="8" t="n"/>
       <c r="F109" s="8" t="n"/>
       <c r="G109" s="8" t="n"/>
+      <c r="H109" s="8" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="7" t="n"/>
@@ -7846,6 +8268,7 @@
       <c r="E110" s="7" t="n"/>
       <c r="F110" s="7" t="n"/>
       <c r="G110" s="7" t="n"/>
+      <c r="H110" s="7" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="8" t="n"/>
@@ -7855,6 +8278,7 @@
       <c r="E111" s="8" t="n"/>
       <c r="F111" s="8" t="n"/>
       <c r="G111" s="8" t="n"/>
+      <c r="H111" s="8" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="7" t="n"/>
@@ -7864,6 +8288,7 @@
       <c r="E112" s="7" t="n"/>
       <c r="F112" s="7" t="n"/>
       <c r="G112" s="7" t="n"/>
+      <c r="H112" s="7" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="8" t="n"/>
@@ -7873,6 +8298,7 @@
       <c r="E113" s="8" t="n"/>
       <c r="F113" s="8" t="n"/>
       <c r="G113" s="8" t="n"/>
+      <c r="H113" s="8" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="7" t="n"/>
@@ -7882,6 +8308,7 @@
       <c r="E114" s="7" t="n"/>
       <c r="F114" s="7" t="n"/>
       <c r="G114" s="7" t="n"/>
+      <c r="H114" s="7" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="8" t="n"/>
@@ -7891,6 +8318,7 @@
       <c r="E115" s="8" t="n"/>
       <c r="F115" s="8" t="n"/>
       <c r="G115" s="8" t="n"/>
+      <c r="H115" s="8" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="7" t="n"/>
@@ -7900,6 +8328,7 @@
       <c r="E116" s="7" t="n"/>
       <c r="F116" s="7" t="n"/>
       <c r="G116" s="7" t="n"/>
+      <c r="H116" s="7" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="8" t="n"/>
@@ -7909,6 +8338,7 @@
       <c r="E117" s="8" t="n"/>
       <c r="F117" s="8" t="n"/>
       <c r="G117" s="8" t="n"/>
+      <c r="H117" s="8" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="7" t="n"/>
@@ -7918,6 +8348,7 @@
       <c r="E118" s="7" t="n"/>
       <c r="F118" s="7" t="n"/>
       <c r="G118" s="7" t="n"/>
+      <c r="H118" s="7" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="8" t="n"/>
@@ -7927,6 +8358,7 @@
       <c r="E119" s="8" t="n"/>
       <c r="F119" s="8" t="n"/>
       <c r="G119" s="8" t="n"/>
+      <c r="H119" s="8" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="7" t="n"/>
@@ -7936,6 +8368,7 @@
       <c r="E120" s="7" t="n"/>
       <c r="F120" s="7" t="n"/>
       <c r="G120" s="7" t="n"/>
+      <c r="H120" s="7" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="8" t="n"/>
@@ -7945,6 +8378,7 @@
       <c r="E121" s="8" t="n"/>
       <c r="F121" s="8" t="n"/>
       <c r="G121" s="8" t="n"/>
+      <c r="H121" s="8" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="7" t="n"/>
@@ -7954,6 +8388,7 @@
       <c r="E122" s="7" t="n"/>
       <c r="F122" s="7" t="n"/>
       <c r="G122" s="7" t="n"/>
+      <c r="H122" s="7" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="8" t="n"/>
@@ -7963,6 +8398,7 @@
       <c r="E123" s="8" t="n"/>
       <c r="F123" s="8" t="n"/>
       <c r="G123" s="8" t="n"/>
+      <c r="H123" s="8" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="7" t="n"/>
@@ -7972,6 +8408,7 @@
       <c r="E124" s="7" t="n"/>
       <c r="F124" s="7" t="n"/>
       <c r="G124" s="7" t="n"/>
+      <c r="H124" s="7" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="8" t="n"/>
@@ -7981,6 +8418,7 @@
       <c r="E125" s="8" t="n"/>
       <c r="F125" s="8" t="n"/>
       <c r="G125" s="8" t="n"/>
+      <c r="H125" s="8" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="7" t="n"/>
@@ -7990,6 +8428,7 @@
       <c r="E126" s="7" t="n"/>
       <c r="F126" s="7" t="n"/>
       <c r="G126" s="7" t="n"/>
+      <c r="H126" s="7" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="8" t="n"/>
@@ -7999,6 +8438,7 @@
       <c r="E127" s="8" t="n"/>
       <c r="F127" s="8" t="n"/>
       <c r="G127" s="8" t="n"/>
+      <c r="H127" s="8" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="7" t="n"/>
@@ -8008,6 +8448,7 @@
       <c r="E128" s="7" t="n"/>
       <c r="F128" s="7" t="n"/>
       <c r="G128" s="7" t="n"/>
+      <c r="H128" s="7" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="8" t="n"/>
@@ -8017,6 +8458,7 @@
       <c r="E129" s="8" t="n"/>
       <c r="F129" s="8" t="n"/>
       <c r="G129" s="8" t="n"/>
+      <c r="H129" s="8" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="7" t="n"/>
@@ -8026,6 +8468,7 @@
       <c r="E130" s="7" t="n"/>
       <c r="F130" s="7" t="n"/>
       <c r="G130" s="7" t="n"/>
+      <c r="H130" s="7" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="8" t="n"/>
@@ -8035,6 +8478,7 @@
       <c r="E131" s="8" t="n"/>
       <c r="F131" s="8" t="n"/>
       <c r="G131" s="8" t="n"/>
+      <c r="H131" s="8" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="7" t="n"/>
@@ -8044,6 +8488,7 @@
       <c r="E132" s="7" t="n"/>
       <c r="F132" s="7" t="n"/>
       <c r="G132" s="7" t="n"/>
+      <c r="H132" s="7" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="8" t="n"/>
@@ -8053,6 +8498,7 @@
       <c r="E133" s="8" t="n"/>
       <c r="F133" s="8" t="n"/>
       <c r="G133" s="8" t="n"/>
+      <c r="H133" s="8" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="7" t="n"/>
@@ -8062,6 +8508,7 @@
       <c r="E134" s="7" t="n"/>
       <c r="F134" s="7" t="n"/>
       <c r="G134" s="7" t="n"/>
+      <c r="H134" s="7" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="8" t="n"/>
@@ -8071,6 +8518,7 @@
       <c r="E135" s="8" t="n"/>
       <c r="F135" s="8" t="n"/>
       <c r="G135" s="8" t="n"/>
+      <c r="H135" s="8" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="7" t="n"/>
@@ -8080,6 +8528,7 @@
       <c r="E136" s="7" t="n"/>
       <c r="F136" s="7" t="n"/>
       <c r="G136" s="7" t="n"/>
+      <c r="H136" s="7" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="8" t="n"/>
@@ -8089,6 +8538,7 @@
       <c r="E137" s="8" t="n"/>
       <c r="F137" s="8" t="n"/>
       <c r="G137" s="8" t="n"/>
+      <c r="H137" s="8" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="7" t="n"/>
@@ -8098,6 +8548,7 @@
       <c r="E138" s="7" t="n"/>
       <c r="F138" s="7" t="n"/>
       <c r="G138" s="7" t="n"/>
+      <c r="H138" s="7" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="8" t="n"/>
@@ -8107,6 +8558,7 @@
       <c r="E139" s="8" t="n"/>
       <c r="F139" s="8" t="n"/>
       <c r="G139" s="8" t="n"/>
+      <c r="H139" s="8" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="7" t="n"/>
@@ -8116,6 +8568,7 @@
       <c r="E140" s="7" t="n"/>
       <c r="F140" s="7" t="n"/>
       <c r="G140" s="7" t="n"/>
+      <c r="H140" s="7" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="8" t="n"/>
@@ -8125,6 +8578,7 @@
       <c r="E141" s="8" t="n"/>
       <c r="F141" s="8" t="n"/>
       <c r="G141" s="8" t="n"/>
+      <c r="H141" s="8" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="7" t="n"/>
@@ -8134,6 +8588,7 @@
       <c r="E142" s="7" t="n"/>
       <c r="F142" s="7" t="n"/>
       <c r="G142" s="7" t="n"/>
+      <c r="H142" s="7" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="8" t="n"/>
@@ -8143,6 +8598,7 @@
       <c r="E143" s="8" t="n"/>
       <c r="F143" s="8" t="n"/>
       <c r="G143" s="8" t="n"/>
+      <c r="H143" s="8" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="7" t="n"/>
@@ -8152,6 +8608,7 @@
       <c r="E144" s="7" t="n"/>
       <c r="F144" s="7" t="n"/>
       <c r="G144" s="7" t="n"/>
+      <c r="H144" s="7" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="8" t="n"/>
@@ -8161,6 +8618,7 @@
       <c r="E145" s="8" t="n"/>
       <c r="F145" s="8" t="n"/>
       <c r="G145" s="8" t="n"/>
+      <c r="H145" s="8" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="7" t="n"/>
@@ -8170,6 +8628,7 @@
       <c r="E146" s="7" t="n"/>
       <c r="F146" s="7" t="n"/>
       <c r="G146" s="7" t="n"/>
+      <c r="H146" s="7" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="8" t="n"/>
@@ -8179,6 +8638,7 @@
       <c r="E147" s="8" t="n"/>
       <c r="F147" s="8" t="n"/>
       <c r="G147" s="8" t="n"/>
+      <c r="H147" s="8" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="7" t="n"/>
@@ -8188,6 +8648,7 @@
       <c r="E148" s="7" t="n"/>
       <c r="F148" s="7" t="n"/>
       <c r="G148" s="7" t="n"/>
+      <c r="H148" s="7" t="n"/>
     </row>
     <row r="149">
       <c r="A149" s="8" t="n"/>
@@ -8197,6 +8658,7 @@
       <c r="E149" s="8" t="n"/>
       <c r="F149" s="8" t="n"/>
       <c r="G149" s="8" t="n"/>
+      <c r="H149" s="8" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="7" t="n"/>
@@ -8206,6 +8668,7 @@
       <c r="E150" s="7" t="n"/>
       <c r="F150" s="7" t="n"/>
       <c r="G150" s="7" t="n"/>
+      <c r="H150" s="7" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="8" t="n"/>
@@ -8215,6 +8678,7 @@
       <c r="E151" s="8" t="n"/>
       <c r="F151" s="8" t="n"/>
       <c r="G151" s="8" t="n"/>
+      <c r="H151" s="8" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="7" t="n"/>
@@ -8224,6 +8688,7 @@
       <c r="E152" s="7" t="n"/>
       <c r="F152" s="7" t="n"/>
       <c r="G152" s="7" t="n"/>
+      <c r="H152" s="7" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="8" t="n"/>
@@ -8233,6 +8698,7 @@
       <c r="E153" s="8" t="n"/>
       <c r="F153" s="8" t="n"/>
       <c r="G153" s="8" t="n"/>
+      <c r="H153" s="8" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="7" t="n"/>
@@ -8242,6 +8708,7 @@
       <c r="E154" s="7" t="n"/>
       <c r="F154" s="7" t="n"/>
       <c r="G154" s="7" t="n"/>
+      <c r="H154" s="7" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="8" t="n"/>
@@ -8251,6 +8718,7 @@
       <c r="E155" s="8" t="n"/>
       <c r="F155" s="8" t="n"/>
       <c r="G155" s="8" t="n"/>
+      <c r="H155" s="8" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="7" t="n"/>
@@ -8260,6 +8728,7 @@
       <c r="E156" s="7" t="n"/>
       <c r="F156" s="7" t="n"/>
       <c r="G156" s="7" t="n"/>
+      <c r="H156" s="7" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="8" t="n"/>
@@ -8269,6 +8738,7 @@
       <c r="E157" s="8" t="n"/>
       <c r="F157" s="8" t="n"/>
       <c r="G157" s="8" t="n"/>
+      <c r="H157" s="8" t="n"/>
     </row>
     <row r="158">
       <c r="A158" s="7" t="n"/>
@@ -8278,6 +8748,7 @@
       <c r="E158" s="7" t="n"/>
       <c r="F158" s="7" t="n"/>
       <c r="G158" s="7" t="n"/>
+      <c r="H158" s="7" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="8" t="n"/>
@@ -8287,6 +8758,7 @@
       <c r="E159" s="8" t="n"/>
       <c r="F159" s="8" t="n"/>
       <c r="G159" s="8" t="n"/>
+      <c r="H159" s="8" t="n"/>
     </row>
     <row r="160">
       <c r="A160" s="7" t="n"/>
@@ -8296,6 +8768,7 @@
       <c r="E160" s="7" t="n"/>
       <c r="F160" s="7" t="n"/>
       <c r="G160" s="7" t="n"/>
+      <c r="H160" s="7" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="8" t="n"/>
@@ -8305,6 +8778,7 @@
       <c r="E161" s="8" t="n"/>
       <c r="F161" s="8" t="n"/>
       <c r="G161" s="8" t="n"/>
+      <c r="H161" s="8" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="7" t="n"/>
@@ -8314,6 +8788,7 @@
       <c r="E162" s="7" t="n"/>
       <c r="F162" s="7" t="n"/>
       <c r="G162" s="7" t="n"/>
+      <c r="H162" s="7" t="n"/>
     </row>
     <row r="163">
       <c r="A163" s="8" t="n"/>
@@ -8323,6 +8798,7 @@
       <c r="E163" s="8" t="n"/>
       <c r="F163" s="8" t="n"/>
       <c r="G163" s="8" t="n"/>
+      <c r="H163" s="8" t="n"/>
     </row>
     <row r="164">
       <c r="A164" s="7" t="n"/>
@@ -8332,6 +8808,7 @@
       <c r="E164" s="7" t="n"/>
       <c r="F164" s="7" t="n"/>
       <c r="G164" s="7" t="n"/>
+      <c r="H164" s="7" t="n"/>
     </row>
     <row r="165">
       <c r="A165" s="8" t="n"/>
@@ -8341,6 +8818,7 @@
       <c r="E165" s="8" t="n"/>
       <c r="F165" s="8" t="n"/>
       <c r="G165" s="8" t="n"/>
+      <c r="H165" s="8" t="n"/>
     </row>
     <row r="166">
       <c r="A166" s="7" t="n"/>
@@ -8350,6 +8828,7 @@
       <c r="E166" s="7" t="n"/>
       <c r="F166" s="7" t="n"/>
       <c r="G166" s="7" t="n"/>
+      <c r="H166" s="7" t="n"/>
     </row>
     <row r="167">
       <c r="A167" s="8" t="n"/>
@@ -8359,6 +8838,7 @@
       <c r="E167" s="8" t="n"/>
       <c r="F167" s="8" t="n"/>
       <c r="G167" s="8" t="n"/>
+      <c r="H167" s="8" t="n"/>
     </row>
     <row r="168">
       <c r="A168" s="7" t="n"/>
@@ -8368,6 +8848,7 @@
       <c r="E168" s="7" t="n"/>
       <c r="F168" s="7" t="n"/>
       <c r="G168" s="7" t="n"/>
+      <c r="H168" s="7" t="n"/>
     </row>
     <row r="169">
       <c r="A169" s="8" t="n"/>
@@ -8377,6 +8858,7 @@
       <c r="E169" s="8" t="n"/>
       <c r="F169" s="8" t="n"/>
       <c r="G169" s="8" t="n"/>
+      <c r="H169" s="8" t="n"/>
     </row>
     <row r="170">
       <c r="A170" s="7" t="n"/>
@@ -8386,6 +8868,7 @@
       <c r="E170" s="7" t="n"/>
       <c r="F170" s="7" t="n"/>
       <c r="G170" s="7" t="n"/>
+      <c r="H170" s="7" t="n"/>
     </row>
     <row r="171">
       <c r="A171" s="8" t="n"/>
@@ -8395,6 +8878,7 @@
       <c r="E171" s="8" t="n"/>
       <c r="F171" s="8" t="n"/>
       <c r="G171" s="8" t="n"/>
+      <c r="H171" s="8" t="n"/>
     </row>
     <row r="172">
       <c r="A172" s="7" t="n"/>
@@ -8404,6 +8888,7 @@
       <c r="E172" s="7" t="n"/>
       <c r="F172" s="7" t="n"/>
       <c r="G172" s="7" t="n"/>
+      <c r="H172" s="7" t="n"/>
     </row>
     <row r="173">
       <c r="A173" s="8" t="n"/>
@@ -8413,6 +8898,7 @@
       <c r="E173" s="8" t="n"/>
       <c r="F173" s="8" t="n"/>
       <c r="G173" s="8" t="n"/>
+      <c r="H173" s="8" t="n"/>
     </row>
     <row r="174">
       <c r="A174" s="7" t="n"/>
@@ -8422,6 +8908,7 @@
       <c r="E174" s="7" t="n"/>
       <c r="F174" s="7" t="n"/>
       <c r="G174" s="7" t="n"/>
+      <c r="H174" s="7" t="n"/>
     </row>
     <row r="175">
       <c r="A175" s="8" t="n"/>
@@ -8431,6 +8918,7 @@
       <c r="E175" s="8" t="n"/>
       <c r="F175" s="8" t="n"/>
       <c r="G175" s="8" t="n"/>
+      <c r="H175" s="8" t="n"/>
     </row>
     <row r="176">
       <c r="A176" s="7" t="n"/>
@@ -8440,6 +8928,7 @@
       <c r="E176" s="7" t="n"/>
       <c r="F176" s="7" t="n"/>
       <c r="G176" s="7" t="n"/>
+      <c r="H176" s="7" t="n"/>
     </row>
     <row r="177">
       <c r="A177" s="8" t="n"/>
@@ -8449,6 +8938,7 @@
       <c r="E177" s="8" t="n"/>
       <c r="F177" s="8" t="n"/>
       <c r="G177" s="8" t="n"/>
+      <c r="H177" s="8" t="n"/>
     </row>
     <row r="178">
       <c r="A178" s="7" t="n"/>
@@ -8458,6 +8948,7 @@
       <c r="E178" s="7" t="n"/>
       <c r="F178" s="7" t="n"/>
       <c r="G178" s="7" t="n"/>
+      <c r="H178" s="7" t="n"/>
     </row>
     <row r="179">
       <c r="A179" s="8" t="n"/>
@@ -8467,6 +8958,7 @@
       <c r="E179" s="8" t="n"/>
       <c r="F179" s="8" t="n"/>
       <c r="G179" s="8" t="n"/>
+      <c r="H179" s="8" t="n"/>
     </row>
     <row r="180">
       <c r="A180" s="7" t="n"/>
@@ -8476,6 +8968,7 @@
       <c r="E180" s="7" t="n"/>
       <c r="F180" s="7" t="n"/>
       <c r="G180" s="7" t="n"/>
+      <c r="H180" s="7" t="n"/>
     </row>
     <row r="181">
       <c r="A181" s="8" t="n"/>
@@ -8485,6 +8978,7 @@
       <c r="E181" s="8" t="n"/>
       <c r="F181" s="8" t="n"/>
       <c r="G181" s="8" t="n"/>
+      <c r="H181" s="8" t="n"/>
     </row>
     <row r="182">
       <c r="A182" s="7" t="n"/>
@@ -8494,6 +8988,7 @@
       <c r="E182" s="7" t="n"/>
       <c r="F182" s="7" t="n"/>
       <c r="G182" s="7" t="n"/>
+      <c r="H182" s="7" t="n"/>
     </row>
     <row r="183">
       <c r="A183" s="8" t="n"/>
@@ -8503,6 +8998,7 @@
       <c r="E183" s="8" t="n"/>
       <c r="F183" s="8" t="n"/>
       <c r="G183" s="8" t="n"/>
+      <c r="H183" s="8" t="n"/>
     </row>
     <row r="184">
       <c r="A184" s="7" t="n"/>
@@ -8512,6 +9008,7 @@
       <c r="E184" s="7" t="n"/>
       <c r="F184" s="7" t="n"/>
       <c r="G184" s="7" t="n"/>
+      <c r="H184" s="7" t="n"/>
     </row>
     <row r="185">
       <c r="A185" s="8" t="n"/>
@@ -8521,6 +9018,7 @@
       <c r="E185" s="8" t="n"/>
       <c r="F185" s="8" t="n"/>
       <c r="G185" s="8" t="n"/>
+      <c r="H185" s="8" t="n"/>
     </row>
     <row r="186">
       <c r="A186" s="7" t="n"/>
@@ -8530,6 +9028,7 @@
       <c r="E186" s="7" t="n"/>
       <c r="F186" s="7" t="n"/>
       <c r="G186" s="7" t="n"/>
+      <c r="H186" s="7" t="n"/>
     </row>
     <row r="187">
       <c r="A187" s="8" t="n"/>
@@ -8539,6 +9038,7 @@
       <c r="E187" s="8" t="n"/>
       <c r="F187" s="8" t="n"/>
       <c r="G187" s="8" t="n"/>
+      <c r="H187" s="8" t="n"/>
     </row>
     <row r="188">
       <c r="A188" s="7" t="n"/>
@@ -8548,6 +9048,7 @@
       <c r="E188" s="7" t="n"/>
       <c r="F188" s="7" t="n"/>
       <c r="G188" s="7" t="n"/>
+      <c r="H188" s="7" t="n"/>
     </row>
     <row r="189">
       <c r="A189" s="8" t="n"/>
@@ -8557,6 +9058,7 @@
       <c r="E189" s="8" t="n"/>
       <c r="F189" s="8" t="n"/>
       <c r="G189" s="8" t="n"/>
+      <c r="H189" s="8" t="n"/>
     </row>
     <row r="190">
       <c r="A190" s="7" t="n"/>
@@ -8566,6 +9068,7 @@
       <c r="E190" s="7" t="n"/>
       <c r="F190" s="7" t="n"/>
       <c r="G190" s="7" t="n"/>
+      <c r="H190" s="7" t="n"/>
     </row>
     <row r="191">
       <c r="A191" s="8" t="n"/>
@@ -8575,6 +9078,7 @@
       <c r="E191" s="8" t="n"/>
       <c r="F191" s="8" t="n"/>
       <c r="G191" s="8" t="n"/>
+      <c r="H191" s="8" t="n"/>
     </row>
     <row r="192">
       <c r="A192" s="7" t="n"/>
@@ -8584,6 +9088,7 @@
       <c r="E192" s="7" t="n"/>
       <c r="F192" s="7" t="n"/>
       <c r="G192" s="7" t="n"/>
+      <c r="H192" s="7" t="n"/>
     </row>
     <row r="193">
       <c r="A193" s="8" t="n"/>
@@ -8593,6 +9098,7 @@
       <c r="E193" s="8" t="n"/>
       <c r="F193" s="8" t="n"/>
       <c r="G193" s="8" t="n"/>
+      <c r="H193" s="8" t="n"/>
     </row>
     <row r="194">
       <c r="A194" s="7" t="n"/>
@@ -8602,6 +9108,7 @@
       <c r="E194" s="7" t="n"/>
       <c r="F194" s="7" t="n"/>
       <c r="G194" s="7" t="n"/>
+      <c r="H194" s="7" t="n"/>
     </row>
     <row r="195">
       <c r="A195" s="8" t="n"/>
@@ -8611,6 +9118,7 @@
       <c r="E195" s="8" t="n"/>
       <c r="F195" s="8" t="n"/>
       <c r="G195" s="8" t="n"/>
+      <c r="H195" s="8" t="n"/>
     </row>
     <row r="196">
       <c r="A196" s="7" t="n"/>
@@ -8620,6 +9128,7 @@
       <c r="E196" s="7" t="n"/>
       <c r="F196" s="7" t="n"/>
       <c r="G196" s="7" t="n"/>
+      <c r="H196" s="7" t="n"/>
     </row>
     <row r="197">
       <c r="A197" s="8" t="n"/>
@@ -8629,6 +9138,7 @@
       <c r="E197" s="8" t="n"/>
       <c r="F197" s="8" t="n"/>
       <c r="G197" s="8" t="n"/>
+      <c r="H197" s="8" t="n"/>
     </row>
     <row r="198">
       <c r="A198" s="7" t="n"/>
@@ -8638,6 +9148,7 @@
       <c r="E198" s="7" t="n"/>
       <c r="F198" s="7" t="n"/>
       <c r="G198" s="7" t="n"/>
+      <c r="H198" s="7" t="n"/>
     </row>
     <row r="199">
       <c r="A199" s="8" t="n"/>
@@ -8647,6 +9158,7 @@
       <c r="E199" s="8" t="n"/>
       <c r="F199" s="8" t="n"/>
       <c r="G199" s="8" t="n"/>
+      <c r="H199" s="8" t="n"/>
     </row>
     <row r="200">
       <c r="A200" s="7" t="n"/>
@@ -8656,6 +9168,7 @@
       <c r="E200" s="7" t="n"/>
       <c r="F200" s="7" t="n"/>
       <c r="G200" s="7" t="n"/>
+      <c r="H200" s="7" t="n"/>
     </row>
     <row r="201">
       <c r="A201" s="8" t="n"/>
@@ -8665,14 +9178,23 @@
       <c r="E201" s="8" t="n"/>
       <c r="F201" s="8" t="n"/>
       <c r="G201" s="8" t="n"/>
+      <c r="H201" s="8" t="n"/>
     </row>
   </sheetData>
-  <dataValidations count="2">
+  <autoFilter ref="A1:H201">
+    <sortState ref="A2:H201">
+      <sortCondition ref="C1:C201"/>
+    </sortState>
+  </autoFilter>
+  <dataValidations count="3">
     <dataValidation sqref="D1" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"email,call,LinkedIn message,coffee chat,thank you,other"</formula1>
     </dataValidation>
     <dataValidation sqref="D2:D1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"email,call,in person, LinkedIn, thank you, other"</formula1>
+    </dataValidation>
+    <dataValidation sqref="G1:G1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+      <formula1>"True,False"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
